--- a/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
   <si>
     <t>RFL</t>
   </si>
@@ -656,140 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -815,25 +823,25 @@
         <v>100</v>
       </c>
       <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
+        <v>100</v>
+      </c>
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1100</v>
-      </c>
-      <c r="P8" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1200</v>
       </c>
       <c r="R8" s="3">
         <v>1200</v>
@@ -842,46 +850,52 @@
         <v>1200</v>
       </c>
       <c r="T8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V8" s="3">
         <v>1400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1000</v>
-      </c>
-      <c r="W8" s="3">
-        <v>1100</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1200</v>
       </c>
       <c r="Y8" s="3">
         <v>1100</v>
       </c>
       <c r="Z8" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="AA8" s="3">
         <v>1100</v>
       </c>
       <c r="AB8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD8" s="3">
         <v>1600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1400</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +986,14 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1084,14 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,80 +1124,82 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>500</v>
+      </c>
+      <c r="F12" s="3">
         <v>1300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>4300</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="M12" s="3">
-        <v>3300</v>
       </c>
       <c r="N12" s="3">
         <v>1600</v>
       </c>
       <c r="O12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1000</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1190,8 +1218,14 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,59 +1316,65 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>79100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>7700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>7000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,11 +1387,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1374,8 +1414,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1407,19 +1453,19 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>400</v>
-      </c>
-      <c r="P15" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>500</v>
       </c>
       <c r="R15" s="3">
         <v>500</v>
@@ -1431,10 +1477,10 @@
         <v>500</v>
       </c>
       <c r="U15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W15" s="3">
         <v>400</v>
@@ -1458,16 +1504,22 @@
         <v>400</v>
       </c>
       <c r="AD15" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="AE15" s="3">
         <v>400</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1549,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F17" s="3">
         <v>2700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>128900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>13100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>16600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>11800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3100</v>
-      </c>
-      <c r="S17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="T17" s="3">
-        <v>4200</v>
       </c>
       <c r="U17" s="3">
         <v>2800</v>
       </c>
       <c r="V17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="W17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="X17" s="3">
         <v>2400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1200</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-5300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-4700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-128700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-12900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-16000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-10800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>200</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,197 +1781,211 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F20" s="3">
         <v>4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>4900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F21" s="3">
         <v>1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-5200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-5700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-127800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-11900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-10000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-7900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>500</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
@@ -1913,29 +1993,29 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
@@ -1943,8 +2023,8 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1967,11 +2047,11 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1979,11 +2059,11 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -1991,100 +2071,112 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F23" s="3">
         <v>1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-128300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-12300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-11100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-8300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-700</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-1400</v>
       </c>
       <c r="Y23" s="3">
         <v>-700</v>
       </c>
       <c r="Z23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-100</v>
       </c>
-      <c r="AC23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>100</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2092,14 +2184,14 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -2149,34 +2241,40 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>8400</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2365,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F26" s="3">
         <v>1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-5200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-128300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-12300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-11100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-8300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-700</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="X26" s="3">
-        <v>1100</v>
       </c>
       <c r="Y26" s="3">
         <v>-700</v>
       </c>
       <c r="Z26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>100</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-5100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-111500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-12200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-10700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-8200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="X27" s="3">
-        <v>1300</v>
       </c>
       <c r="Y27" s="3">
         <v>-500</v>
       </c>
       <c r="Z27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>100</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,80 +2659,86 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>-200</v>
-      </c>
       <c r="G29" s="3">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>-200</v>
       </c>
       <c r="I29" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K29" s="3">
         <v>-600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-1500</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,8 +2757,14 @@
       <c r="AF29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2855,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2953,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-4900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F33" s="3">
         <v>1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-112000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-12400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-12200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-8200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-1200</v>
       </c>
       <c r="Y33" s="3">
         <v>-500</v>
       </c>
       <c r="Z33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>100</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3247,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F35" s="3">
         <v>1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-112000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-12400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-12200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-8200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-1200</v>
       </c>
       <c r="Y35" s="3">
         <v>-500</v>
       </c>
       <c r="Z35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>100</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3488,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,89 +3524,91 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F41" s="3">
         <v>21500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>22200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>26500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>29000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>65000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>72400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>6200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>8400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>10800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>12000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>13000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>14800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>10100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>15800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>10600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>12000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>11500</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,35 +3618,41 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>58900</v>
+      </c>
+      <c r="F42" s="3">
         <v>58000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>67000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>79200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>71000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>36700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>30400</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3485,11 +3665,11 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3507,20 +3687,20 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>20100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>24700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>30900</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,88 +3716,94 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="E43" s="3">
         <v>2500</v>
       </c>
       <c r="F43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3600</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>200</v>
       </c>
       <c r="AA43" s="3">
         <v>400</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
+      <c r="AB43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>400</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>3</v>
@@ -3628,8 +3814,14 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,89 +3912,95 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>44700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>5800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>6000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>500</v>
-      </c>
-      <c r="T45" s="3">
-        <v>500</v>
       </c>
       <c r="U45" s="3">
         <v>500</v>
       </c>
       <c r="V45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W45" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="X45" s="3">
         <v>400</v>
       </c>
       <c r="Y45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA45" s="3">
         <v>2200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3812,89 +4010,95 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>75100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>77500</v>
+      </c>
+      <c r="F46" s="3">
         <v>82900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>85000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>90000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>94900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>108300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>62500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>71500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>78500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>14800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>6700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>9800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>9200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>10300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>11700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>13300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>14600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>15700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>34400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>44500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>44200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>12400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>12000</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,89 +4108,95 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F47" s="3">
         <v>12600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>8000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>5300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>5000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>5200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>5200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>6000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>93000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>93500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>92700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>79100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>78900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>77400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>77700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>77100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>77100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>76700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>76200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>29600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>19500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>17600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>11700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>13000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,13 +4206,19 @@
       <c r="AF47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="E48" s="3">
         <v>1700</v>
@@ -4011,74 +4227,74 @@
         <v>1700</v>
       </c>
       <c r="G48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I48" s="3">
         <v>1800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>42200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>42500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>42900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>43200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>43600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>43800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>44100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>44400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>47800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>48300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>48600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>48700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>49200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>49400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>49700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>50100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>50600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>51000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>51000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,13 +4304,19 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1600</v>
+        <v>7000</v>
       </c>
       <c r="E49" s="3">
         <v>1600</v>
@@ -4145,10 +4367,10 @@
         <v>1600</v>
       </c>
       <c r="U49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="V49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="W49" s="3">
         <v>1700</v>
@@ -4157,16 +4379,16 @@
         <v>1700</v>
       </c>
       <c r="Y49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="Z49" s="3">
         <v>1700</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
+      <c r="AA49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>1700</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
@@ -4180,8 +4402,14 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4500,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4598,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4382,19 +4622,19 @@
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
         <v>1400</v>
       </c>
       <c r="K52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="L52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="M52" s="3">
         <v>1500</v>
@@ -4403,50 +4643,50 @@
         <v>1500</v>
       </c>
       <c r="O52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>1500</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1500</v>
       </c>
       <c r="S52" s="3">
         <v>1500</v>
       </c>
       <c r="T52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V52" s="3">
         <v>1400</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V52" s="3">
-        <v>1200</v>
       </c>
       <c r="W52" s="3">
         <v>1200</v>
       </c>
       <c r="X52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>700</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4456,8 +4696,14 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,89 +4794,95 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>95500</v>
+      </c>
+      <c r="F54" s="3">
         <v>98800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>96400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>98600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>103200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>118300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>112800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>122600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>130400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>154100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>146200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>146200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>134600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>136300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>137400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>139200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>140400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>142100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>143500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>144200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>116600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>116900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>115100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>77600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>76600</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,8 +4892,14 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4932,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,89 +4968,91 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E57" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F57" s="3">
         <v>400</v>
       </c>
       <c r="G57" s="3">
+        <v>600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>400</v>
+      </c>
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>100</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4800,16 +5062,22 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
+        <v>1700</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -4818,26 +5086,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>15000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>14900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>14800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>14700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>14500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4850,11 +5118,11 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -4892,88 +5160,94 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>400</v>
+      </c>
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>10300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>800</v>
-      </c>
-      <c r="R59" s="3">
-        <v>600</v>
-      </c>
-      <c r="S59" s="3">
-        <v>600</v>
       </c>
       <c r="T59" s="3">
         <v>600</v>
       </c>
       <c r="U59" s="3">
+        <v>600</v>
+      </c>
+      <c r="V59" s="3">
+        <v>600</v>
+      </c>
+      <c r="W59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>500</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>400</v>
       </c>
       <c r="AA59" s="3">
         <v>300</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
+      <c r="AB59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>300</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
@@ -4984,89 +5258,95 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>900</v>
+      </c>
+      <c r="F60" s="3">
         <v>2100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>21000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>17800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>22800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>17300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>17300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>10800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1200</v>
-      </c>
-      <c r="W60" s="3">
-        <v>700</v>
-      </c>
-      <c r="X60" s="3">
-        <v>900</v>
       </c>
       <c r="Y60" s="3">
         <v>700</v>
       </c>
       <c r="Z60" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB60" s="3">
         <v>500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>400</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5076,8 +5356,14 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5130,19 +5416,19 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>14900</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -5168,28 +5454,34 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
@@ -5198,10 +5490,10 @@
         <v>100</v>
       </c>
       <c r="L62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -5210,47 +5502,47 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
       </c>
       <c r="S62" s="3">
+        <v>100</v>
+      </c>
+      <c r="T62" s="3">
+        <v>100</v>
+      </c>
+      <c r="U62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB62" s="3">
         <v>24500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>23500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5260,8 +5552,14 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5650,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5748,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,13 +5846,19 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>1200</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>3</v>
@@ -5553,72 +5869,72 @@
       <c r="G66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
         <v>17800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>19700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>31700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>31800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>19400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>25400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>19000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>19500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>15400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>15200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>15200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>31200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>25500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>25300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>10200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>10200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>9600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>34700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>33200</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5628,8 +5944,14 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5984,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6078,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6176,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6274,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,83 +6372,89 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-164900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-171000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-167300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-168600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-167100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-163900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-165500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-160700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-155100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-170100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-40800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-28400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-25900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-17700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-10900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-8700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-7400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-5800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-3700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-2600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-1600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-200</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6122,8 +6470,14 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6568,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6666,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,89 +6764,95 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>98200</v>
+      </c>
+      <c r="F76" s="3">
         <v>100300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>98500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>100100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>103400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>100500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>98100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>102900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>98700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>122300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>126800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>120800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>115600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>116800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>122100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>124100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>125200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>111000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>118000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>118800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>106400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>106700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>105400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>42900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>43400</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6862,14 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6960,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F81" s="3">
         <v>1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-112000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-12400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-12200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-8200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-1200</v>
       </c>
       <c r="Y81" s="3">
         <v>-500</v>
       </c>
       <c r="Z81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>100</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7201,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6823,13 +7221,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>-1100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>400</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
@@ -6838,19 +7236,19 @@
         <v>400</v>
       </c>
       <c r="M83" s="3">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="N83" s="3">
         <v>400</v>
       </c>
       <c r="O83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P83" s="3">
         <v>400</v>
       </c>
-      <c r="P83" s="3">
-        <v>500</v>
-      </c>
       <c r="Q83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>500</v>
@@ -6862,10 +7260,10 @@
         <v>500</v>
       </c>
       <c r="U83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W83" s="3">
         <v>400</v>
@@ -6889,16 +7287,22 @@
         <v>400</v>
       </c>
       <c r="AD83" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="AE83" s="3">
         <v>400</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7393,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7491,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7589,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7687,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7785,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-5600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-10400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-7300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-6500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-7000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-8600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>100</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7923,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7495,11 +7937,11 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -7516,28 +7958,28 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-300</v>
@@ -7546,37 +7988,43 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-700</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8115,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8213,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F94" s="3">
         <v>7400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>7400</v>
       </c>
-      <c r="F94" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>13900</v>
-      </c>
       <c r="H94" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>14000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-6400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-30500</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-26900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-8700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-12100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>3600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
       </c>
       <c r="U94" s="3">
         <v>-300</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X94" s="3">
         <v>-25700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-5200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>4200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8351,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8445,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8543,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8641,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,136 +8739,148 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-15000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>6000</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>97900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>14500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>15800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>13800</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>30700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>900</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>2500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>19300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>18400</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
       </c>
       <c r="G101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>100</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
@@ -8399,16 +8897,16 @@
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>-100</v>
@@ -8417,7 +8915,7 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -8434,99 +8932,111 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F102" s="3">
         <v>6100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>5800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-13200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-41100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-7400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>64500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>8200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>4700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-5700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>5200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>9500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>9600</v>
       </c>
-      <c r="AF102" s="3" t="s">
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
@@ -656,153 +656,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -829,22 +832,22 @@
         <v>100</v>
       </c>
       <c r="M8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N8" s="3">
         <v>200</v>
       </c>
       <c r="O8" s="3">
+        <v>200</v>
+      </c>
+      <c r="P8" s="3">
         <v>600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1100</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1200</v>
       </c>
       <c r="S8" s="3">
         <v>1200</v>
@@ -856,51 +859,54 @@
         <v>1200</v>
       </c>
       <c r="V8" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="W8" s="3">
         <v>1400</v>
       </c>
       <c r="X8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y8" s="3">
         <v>1000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1400</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>100</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
@@ -992,13 +998,16 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>200</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
@@ -1090,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,83 +1138,84 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>100</v>
-      </c>
-      <c r="W12" s="3">
-        <v>300</v>
       </c>
       <c r="X12" s="3">
         <v>300</v>
       </c>
       <c r="Y12" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z12" s="3">
         <v>400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1000</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,32 +1338,35 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1600</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>100</v>
       </c>
       <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1355,29 +1374,29 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>79100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>7700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1393,8 +1412,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1420,13 +1439,16 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1459,16 +1481,16 @@
         <v>0</v>
       </c>
       <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
         <v>100</v>
-      </c>
-      <c r="P15" s="3">
-        <v>400</v>
       </c>
       <c r="Q15" s="3">
         <v>400</v>
       </c>
       <c r="R15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S15" s="3">
         <v>500</v>
@@ -1483,7 +1505,7 @@
         <v>500</v>
       </c>
       <c r="W15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="X15" s="3">
         <v>400</v>
@@ -1510,16 +1532,19 @@
         <v>400</v>
       </c>
       <c r="AF15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG15" s="3">
         <v>800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>400</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E17" s="3">
         <v>4800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>128900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2500</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>1800</v>
       </c>
       <c r="AB17" s="3">
         <v>1800</v>
       </c>
       <c r="AC17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AD17" s="3">
         <v>2200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1200</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-128700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2800</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-1400</v>
       </c>
       <c r="X18" s="3">
         <v>-1400</v>
       </c>
       <c r="Y18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>200</v>
       </c>
       <c r="AG18" s="3">
         <v>200</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,251 +1815,258 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E20" s="3">
         <v>10900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
       </c>
       <c r="AC20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>100</v>
       </c>
       <c r="AF20" s="3">
         <v>100</v>
       </c>
       <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-64700</v>
+      </c>
+      <c r="E21" s="3">
         <v>6100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-127800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-700</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-300</v>
       </c>
       <c r="Y21" s="3">
         <v>-300</v>
       </c>
       <c r="Z21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>500</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>100</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>100</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>100</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -2053,8 +2092,8 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -2065,8 +2104,8 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2077,111 +2116,117 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="E23" s="3">
         <v>6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-128300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1200</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-700</v>
       </c>
       <c r="Y23" s="3">
         <v>-700</v>
       </c>
       <c r="Z23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-700</v>
       </c>
       <c r="AB23" s="3">
         <v>-700</v>
       </c>
       <c r="AC23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-100</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
         <v>300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>100</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -2190,11 +2235,11 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -2247,20 +2292,20 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>8400</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
@@ -2270,11 +2315,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-62300</v>
+      </c>
+      <c r="E26" s="3">
         <v>6100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-128300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-700</v>
       </c>
       <c r="Y26" s="3">
         <v>-700</v>
       </c>
       <c r="Z26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AA26" s="3">
         <v>1100</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-700</v>
       </c>
       <c r="AB26" s="3">
         <v>-700</v>
       </c>
       <c r="AC26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-100</v>
       </c>
       <c r="AE26" s="3">
         <v>-100</v>
       </c>
       <c r="AF26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG26" s="3">
         <v>300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>100</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E27" s="3">
         <v>6000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-111500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2200</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-1000</v>
       </c>
       <c r="X27" s="3">
         <v>-1000</v>
       </c>
       <c r="Y27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-500</v>
       </c>
       <c r="AB27" s="3">
         <v>-500</v>
       </c>
       <c r="AC27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-100</v>
       </c>
       <c r="AE27" s="3">
         <v>-100</v>
       </c>
       <c r="AF27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>100</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2677,40 +2737,40 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>6700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-600</v>
-      </c>
-      <c r="L29" s="3">
-        <v>-500</v>
       </c>
       <c r="M29" s="3">
         <v>-500</v>
       </c>
       <c r="N29" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O29" s="3">
         <v>-200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-1500</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2718,17 +2778,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
+      <c r="V29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
@@ -2736,12 +2796,12 @@
       <c r="Y29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
       <c r="AC32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>200</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-100</v>
       </c>
       <c r="AF32" s="3">
         <v>-100</v>
       </c>
       <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E33" s="3">
         <v>6000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-112000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2200</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-1000</v>
       </c>
       <c r="X33" s="3">
         <v>-1000</v>
       </c>
       <c r="Y33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-500</v>
       </c>
       <c r="AB33" s="3">
         <v>-500</v>
       </c>
       <c r="AC33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-100</v>
       </c>
       <c r="AE33" s="3">
         <v>-100</v>
       </c>
       <c r="AF33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>100</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E35" s="3">
         <v>6000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-112000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2200</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-1000</v>
       </c>
       <c r="X35" s="3">
         <v>-1000</v>
       </c>
       <c r="Y35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-500</v>
       </c>
       <c r="AB35" s="3">
         <v>-500</v>
       </c>
       <c r="AC35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-100</v>
       </c>
       <c r="AE35" s="3">
         <v>-100</v>
       </c>
       <c r="AF35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>100</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,92 +3611,93 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E41" s="3">
         <v>7100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>29000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>65000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>72400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11500</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3624,38 +3710,41 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E42" s="3">
         <v>64600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>58900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>58000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>67000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>79200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>71000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>36700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>30400</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3671,8 +3760,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3693,17 +3782,17 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
         <v>20100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>24700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>30900</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,16 +3811,19 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2900</v>
-      </c>
-      <c r="E43" s="3">
-        <v>2500</v>
       </c>
       <c r="F43" s="3">
         <v>2500</v>
@@ -3740,74 +3832,74 @@
         <v>2500</v>
       </c>
       <c r="H43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1000</v>
-      </c>
-      <c r="L43" s="3">
-        <v>700</v>
       </c>
       <c r="M43" s="3">
         <v>700</v>
       </c>
       <c r="N43" s="3">
+        <v>700</v>
+      </c>
+      <c r="O43" s="3">
         <v>900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>800</v>
-      </c>
-      <c r="P43" s="3">
-        <v>600</v>
       </c>
       <c r="Q43" s="3">
         <v>600</v>
       </c>
       <c r="R43" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="S43" s="3">
         <v>400</v>
       </c>
       <c r="T43" s="3">
+        <v>400</v>
+      </c>
+      <c r="U43" s="3">
         <v>500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>400</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3820,8 +3912,11 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3918,64 +4013,67 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3200</v>
-      </c>
-      <c r="S45" s="3">
-        <v>300</v>
       </c>
       <c r="T45" s="3">
         <v>300</v>
       </c>
       <c r="U45" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="V45" s="3">
         <v>500</v>
@@ -3984,26 +4082,26 @@
         <v>500</v>
       </c>
       <c r="X45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y45" s="3">
         <v>400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4016,92 +4114,95 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E46" s="3">
         <v>75100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>77500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>82900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>85000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>90000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>94900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>108300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>62500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>71500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>78500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>34400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>44500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>44200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12000</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4114,92 +4215,95 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E47" s="3">
         <v>21900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>5200</v>
       </c>
       <c r="K47" s="3">
         <v>5200</v>
       </c>
       <c r="L47" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M47" s="3">
         <v>5500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>93000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>93500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>92700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>79100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>78900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>77400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>77700</v>
-      </c>
-      <c r="U47" s="3">
-        <v>77100</v>
       </c>
       <c r="V47" s="3">
         <v>77100</v>
       </c>
       <c r="W47" s="3">
+        <v>77100</v>
+      </c>
+      <c r="X47" s="3">
         <v>76700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>76200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>29600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>19500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>17600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>11700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4212,16 +4316,19 @@
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2100</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1700</v>
       </c>
       <c r="F48" s="3">
         <v>1700</v>
@@ -4233,70 +4340,70 @@
         <v>1700</v>
       </c>
       <c r="I48" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="J48" s="3">
         <v>1800</v>
       </c>
       <c r="K48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L48" s="3">
         <v>42200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>43800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>44100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>44400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>47800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>48300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>48600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>48700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>49200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>49400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>49700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>50100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>50600</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>51000</v>
       </c>
       <c r="AC48" s="3">
         <v>51000</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
+      <c r="AD48" s="3">
+        <v>51000</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
@@ -4310,8 +4417,11 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4319,7 +4429,7 @@
         <v>7000</v>
       </c>
       <c r="E49" s="3">
-        <v>1600</v>
+        <v>7000</v>
       </c>
       <c r="F49" s="3">
         <v>1600</v>
@@ -4373,7 +4483,7 @@
         <v>1600</v>
       </c>
       <c r="W49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="X49" s="3">
         <v>1700</v>
@@ -4385,14 +4495,14 @@
         <v>1700</v>
       </c>
       <c r="AA49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB49" s="3">
         <v>1800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1700</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4408,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,13 +4720,16 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -4628,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>1400</v>
@@ -4637,7 +4756,7 @@
         <v>1400</v>
       </c>
       <c r="M52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="N52" s="3">
         <v>1500</v>
@@ -4649,13 +4768,13 @@
         <v>1500</v>
       </c>
       <c r="Q52" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="R52" s="3">
         <v>1600</v>
       </c>
       <c r="S52" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="T52" s="3">
         <v>1500</v>
@@ -4664,10 +4783,10 @@
         <v>1500</v>
       </c>
       <c r="V52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W52" s="3">
         <v>1400</v>
-      </c>
-      <c r="W52" s="3">
-        <v>1200</v>
       </c>
       <c r="X52" s="3">
         <v>1200</v>
@@ -4676,20 +4795,20 @@
         <v>1200</v>
       </c>
       <c r="Z52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>700</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,92 +4922,95 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E54" s="3">
         <v>106100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>95500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>98800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>96400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>98600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>103200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>118300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>112800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>122600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>130400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>154100</v>
-      </c>
-      <c r="O54" s="3">
-        <v>146200</v>
       </c>
       <c r="P54" s="3">
         <v>146200</v>
       </c>
       <c r="Q54" s="3">
+        <v>146200</v>
+      </c>
+      <c r="R54" s="3">
         <v>134600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>136300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>137400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>139200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>140400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>142100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>143500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>144200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>116600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>116900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>115100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>77600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>76600</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4898,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,91 +5099,92 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1200</v>
       </c>
       <c r="M57" s="3">
         <v>1200</v>
       </c>
       <c r="N57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>700</v>
-      </c>
-      <c r="T57" s="3">
-        <v>600</v>
       </c>
       <c r="U57" s="3">
         <v>600</v>
       </c>
       <c r="V57" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="W57" s="3">
         <v>800</v>
       </c>
       <c r="X57" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>400</v>
       </c>
       <c r="AA57" s="3">
         <v>400</v>
       </c>
       <c r="AB57" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AC57" s="3">
         <v>100</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
+      <c r="AD57" s="3">
+        <v>100</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
@@ -5068,19 +5198,22 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1700</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -5092,23 +5225,23 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>15000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5124,8 +5257,8 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -5166,61 +5299,64 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
-      </c>
-      <c r="T59" s="3">
-        <v>600</v>
       </c>
       <c r="U59" s="3">
         <v>600</v>
@@ -5229,29 +5365,29 @@
         <v>600</v>
       </c>
       <c r="W59" s="3">
+        <v>600</v>
+      </c>
+      <c r="X59" s="3">
         <v>200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>300</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5264,92 +5400,95 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22800</v>
-      </c>
-      <c r="M60" s="3">
-        <v>17300</v>
       </c>
       <c r="N60" s="3">
         <v>17300</v>
       </c>
       <c r="O60" s="3">
+        <v>17300</v>
+      </c>
+      <c r="P60" s="3">
         <v>4900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1500</v>
-      </c>
-      <c r="T60" s="3">
-        <v>1200</v>
       </c>
       <c r="U60" s="3">
         <v>1200</v>
       </c>
       <c r="V60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W60" s="3">
         <v>1400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>400</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5362,13 +5501,16 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -5422,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>14900</v>
@@ -5431,7 +5573,7 @@
         <v>14900</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="Z61" s="3">
         <v>0</v>
@@ -5460,16 +5602,19 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>100</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
@@ -5478,13 +5623,13 @@
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
       </c>
       <c r="J62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K62" s="3">
         <v>100</v>
@@ -5496,7 +5641,7 @@
         <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -5508,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
@@ -5517,35 +5662,35 @@
         <v>100</v>
       </c>
       <c r="U62" s="3">
+        <v>100</v>
+      </c>
+      <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>500</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC62" s="3">
         <v>24500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>23500</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5558,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,17 +6006,20 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1200</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5875,69 +6032,69 @@
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
         <v>17800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15400</v>
-      </c>
-      <c r="T66" s="3">
-        <v>15200</v>
       </c>
       <c r="U66" s="3">
         <v>15200</v>
       </c>
       <c r="V66" s="3">
+        <v>15200</v>
+      </c>
+      <c r="W66" s="3">
         <v>31200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>25500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25300</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>10200</v>
       </c>
       <c r="Z66" s="3">
         <v>10200</v>
       </c>
       <c r="AA66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="AB66" s="3">
         <v>9600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>33200</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5950,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,86 +6548,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-197300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-164900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-171000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-167300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-168600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-167100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-163900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-165500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-160700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-155100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-170100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-40800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-28400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-17700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-16300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-10900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6476,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,92 +6952,95 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E76" s="3">
         <v>104900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>98200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>100300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>98500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>100100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>103400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>100500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>98100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>102900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>98700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>122300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>126800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>120800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>115600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>116800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>122100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>124100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>125200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>111000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>118000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>118800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>106400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>106700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>105400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>42900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>43400</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6868,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E81" s="3">
         <v>6000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-112000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2200</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-1000</v>
       </c>
       <c r="X81" s="3">
         <v>-1000</v>
       </c>
       <c r="Y81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-500</v>
       </c>
       <c r="AB81" s="3">
         <v>-500</v>
       </c>
       <c r="AC81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-100</v>
       </c>
       <c r="AE81" s="3">
         <v>-100</v>
       </c>
       <c r="AF81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>100</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,13 +7400,14 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -7227,10 +7425,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>-1100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
@@ -7242,16 +7440,16 @@
         <v>400</v>
       </c>
       <c r="O83" s="3">
+        <v>400</v>
+      </c>
+      <c r="P83" s="3">
         <v>1100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>400</v>
       </c>
       <c r="Q83" s="3">
         <v>400</v>
       </c>
       <c r="R83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S83" s="3">
         <v>500</v>
@@ -7266,7 +7464,7 @@
         <v>500</v>
       </c>
       <c r="W83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="X83" s="3">
         <v>400</v>
@@ -7293,16 +7491,19 @@
         <v>400</v>
       </c>
       <c r="AF83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG83" s="3">
         <v>800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>400</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-700</v>
       </c>
       <c r="Z89" s="3">
         <v>-700</v>
       </c>
       <c r="AA89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>100</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
       <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-200</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,13 +8144,14 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7940,11 +8160,11 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -7964,67 +8184,70 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-200</v>
       </c>
       <c r="AD91" s="3">
         <v>-200</v>
       </c>
       <c r="AE91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-700</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6800</v>
-      </c>
-      <c r="F94" s="3">
-        <v>7400</v>
       </c>
       <c r="G94" s="3">
         <v>7400</v>
       </c>
       <c r="H94" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-7600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>14000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30500</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-26900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>4200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8451,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,53 +8987,56 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>800</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6000</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>97900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>14500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>15800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>13800</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
@@ -8799,11 +9044,11 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -8811,79 +9056,82 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>30700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>2500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>19300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>18400</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-100</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
       </c>
       <c r="K101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
@@ -8903,23 +9151,23 @@
         <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
@@ -8938,105 +9186,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-41100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>64500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>9500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>9600</v>
       </c>
-      <c r="AH102" s="3" t="s">
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
   <si>
     <t>RFL</t>
   </si>
@@ -656,159 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42766</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
         <v>300</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
@@ -835,22 +839,22 @@
         <v>100</v>
       </c>
       <c r="N8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>200</v>
       </c>
       <c r="P8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q8" s="3">
         <v>600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1100</v>
-      </c>
-      <c r="S8" s="3">
-        <v>1200</v>
       </c>
       <c r="T8" s="3">
         <v>1200</v>
@@ -862,54 +866,57 @@
         <v>1200</v>
       </c>
       <c r="W8" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="X8" s="3">
         <v>1400</v>
       </c>
       <c r="Y8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z8" s="3">
         <v>1000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1400</v>
       </c>
-      <c r="AI8" s="3" t="s">
+      <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+      <c r="E9" s="3">
+        <v>100</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
@@ -1001,31 +1008,34 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,86 +1152,87 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E12" s="3">
         <v>91400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
+        <v>600</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I12" s="3">
+        <v>700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S12" s="3">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>700</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M12" s="3">
-        <v>3300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>4300</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="P12" s="3">
-        <v>3300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="R12" s="3">
-        <v>500</v>
-      </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>100</v>
-      </c>
-      <c r="X12" s="3">
-        <v>300</v>
       </c>
       <c r="Y12" s="3">
         <v>300</v>
       </c>
       <c r="Z12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA12" s="3">
         <v>400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1000</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,35 +1358,38 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="E14" s="3">
-        <v>1600</v>
+        <v>3500</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-8500</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-3400</v>
       </c>
       <c r="H14" s="3">
-        <v>100</v>
+        <v>-3400</v>
       </c>
       <c r="I14" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1377,29 +1397,29 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>79100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>7700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1415,8 +1435,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1442,8 +1462,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1451,7 +1474,7 @@
         <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1484,16 +1507,16 @@
         <v>0</v>
       </c>
       <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
         <v>100</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>400</v>
       </c>
       <c r="R15" s="3">
         <v>400</v>
       </c>
       <c r="S15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T15" s="3">
         <v>500</v>
@@ -1508,7 +1531,7 @@
         <v>500</v>
       </c>
       <c r="X15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Y15" s="3">
         <v>400</v>
@@ -1535,16 +1558,19 @@
         <v>400</v>
       </c>
       <c r="AG15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH15" s="3">
         <v>800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>400</v>
       </c>
-      <c r="AI15" s="3" t="s">
+      <c r="AJ15" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>93500</v>
+        <v>3300</v>
       </c>
       <c r="E17" s="3">
+        <v>62200</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M17" s="3">
         <v>4800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="N17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O17" s="3">
+        <v>128900</v>
+      </c>
+      <c r="P17" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>16600</v>
+      </c>
+      <c r="R17" s="3">
+        <v>11800</v>
+      </c>
+      <c r="S17" s="3">
+        <v>4300</v>
+      </c>
+      <c r="T17" s="3">
+        <v>4800</v>
+      </c>
+      <c r="U17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="W17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="X17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AB17" s="3">
         <v>2500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5400</v>
-      </c>
-      <c r="K17" s="3">
-        <v>4900</v>
-      </c>
-      <c r="L17" s="3">
-        <v>4800</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>128900</v>
-      </c>
-      <c r="O17" s="3">
-        <v>13100</v>
-      </c>
-      <c r="P17" s="3">
-        <v>16600</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>11800</v>
-      </c>
-      <c r="R17" s="3">
-        <v>4300</v>
-      </c>
-      <c r="S17" s="3">
-        <v>4800</v>
-      </c>
-      <c r="T17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="U17" s="3">
-        <v>3100</v>
-      </c>
-      <c r="V17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="W17" s="3">
-        <v>4200</v>
-      </c>
-      <c r="X17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>2400</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>2300</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>1800</v>
       </c>
       <c r="AC17" s="3">
         <v>1800</v>
       </c>
       <c r="AD17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AE17" s="3">
         <v>2200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1200</v>
       </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-93200</v>
+        <v>-3100</v>
       </c>
       <c r="E18" s="3">
+        <v>-61900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="M18" s="3">
         <v>-4700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-128700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2800</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-1400</v>
       </c>
       <c r="Y18" s="3">
         <v>-1400</v>
       </c>
       <c r="Z18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>200</v>
       </c>
       <c r="AH18" s="3">
         <v>200</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AI18" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,260 +1849,267 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>28400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>10900</v>
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>-1100</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3">
-        <v>4000</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
       </c>
       <c r="AD20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>100</v>
       </c>
       <c r="AG20" s="3">
         <v>100</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-64700</v>
+        <v>-3100</v>
       </c>
       <c r="E21" s="3">
-        <v>6100</v>
+        <v>-61800</v>
       </c>
       <c r="F21" s="3">
-        <v>-3500</v>
+        <v>-3300</v>
       </c>
       <c r="G21" s="3">
-        <v>1500</v>
+        <v>-2900</v>
       </c>
       <c r="H21" s="3">
-        <v>-1700</v>
+        <v>-3100</v>
       </c>
       <c r="I21" s="3">
-        <v>-3200</v>
+        <v>-3000</v>
       </c>
       <c r="J21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-5200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-127800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-300</v>
       </c>
       <c r="Z21" s="3">
         <v>-300</v>
       </c>
       <c r="AA21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>500</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>100</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -2095,8 +2135,8 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
@@ -2107,8 +2147,8 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
@@ -2119,130 +2159,136 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-64900</v>
       </c>
-      <c r="E23" s="3">
-        <v>6100</v>
-      </c>
       <c r="F23" s="3">
-        <v>-3500</v>
+        <v>5900</v>
       </c>
       <c r="G23" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="H23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-128300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-700</v>
       </c>
       <c r="Z23" s="3">
         <v>-700</v>
       </c>
       <c r="AA23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-700</v>
       </c>
       <c r="AC23" s="3">
         <v>-700</v>
       </c>
       <c r="AD23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-100</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
       <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
         <v>300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3" t="s">
+      <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2600</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -2295,20 +2341,20 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>8400</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
@@ -2318,11 +2364,14 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-      <c r="AI24" s="3" t="s">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-62300</v>
       </c>
-      <c r="E26" s="3">
-        <v>6100</v>
-      </c>
       <c r="F26" s="3">
-        <v>-3500</v>
+        <v>5900</v>
       </c>
       <c r="G26" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="H26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-128300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-700</v>
       </c>
       <c r="Z26" s="3">
         <v>-700</v>
       </c>
       <c r="AA26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB26" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-700</v>
       </c>
       <c r="AC26" s="3">
         <v>-700</v>
       </c>
       <c r="AD26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-100</v>
       </c>
       <c r="AF26" s="3">
         <v>-100</v>
       </c>
       <c r="AG26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH26" s="3">
         <v>300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>100</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-32400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-3600</v>
-      </c>
       <c r="G27" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="H27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1400</v>
       </c>
-      <c r="I27" s="3">
-        <v>-3100</v>
-      </c>
       <c r="J27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-111500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y27" s="3">
         <v>-1000</v>
       </c>
       <c r="Z27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1300</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-500</v>
       </c>
       <c r="AC27" s="3">
         <v>-500</v>
       </c>
       <c r="AD27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-100</v>
       </c>
       <c r="AF27" s="3">
         <v>-100</v>
       </c>
       <c r="AG27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH27" s="3">
         <v>300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>100</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2740,40 +2801,40 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-100</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>6700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-600</v>
-      </c>
-      <c r="M29" s="3">
-        <v>-500</v>
       </c>
       <c r="N29" s="3">
         <v>-500</v>
       </c>
       <c r="O29" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P29" s="3">
         <v>-200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2781,17 +2842,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>3</v>
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>3</v>
@@ -2799,12 +2860,12 @@
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-28400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-10900</v>
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>1100</v>
+        <v>-200</v>
       </c>
       <c r="G32" s="3">
-        <v>-4000</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
       </c>
       <c r="AD32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-100</v>
       </c>
       <c r="AG32" s="3">
         <v>-100</v>
       </c>
       <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-32400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-3600</v>
       </c>
       <c r="G33" s="3">
         <v>1200</v>
       </c>
       <c r="H33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-112000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y33" s="3">
         <v>-1000</v>
       </c>
       <c r="Z33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-500</v>
       </c>
       <c r="AC33" s="3">
         <v>-500</v>
       </c>
       <c r="AD33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-100</v>
       </c>
       <c r="AF33" s="3">
         <v>-100</v>
       </c>
       <c r="AG33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH33" s="3">
         <v>300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>100</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-32400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-3600</v>
       </c>
       <c r="G35" s="3">
         <v>1200</v>
       </c>
       <c r="H35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-112000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y35" s="3">
         <v>-1000</v>
       </c>
       <c r="Z35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-500</v>
       </c>
       <c r="AC35" s="3">
         <v>-500</v>
       </c>
       <c r="AD35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-100</v>
       </c>
       <c r="AF35" s="3">
         <v>-100</v>
       </c>
       <c r="AG35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH35" s="3">
         <v>300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>100</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42766</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
-      <c r="AI38" s="2" t="s">
+      <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,95 +3698,96 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E41" s="3">
         <v>7400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7100</v>
       </c>
-      <c r="F41" s="3">
-        <v>13200</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3">
         <v>21500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>29000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>65000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>72400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>14800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>15800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11500</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3713,41 +3800,44 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>64600</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>58900</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>71000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>30400</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3763,8 +3853,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3785,17 +3875,17 @@
         <v>0</v>
       </c>
       <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
         <v>20100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>24700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>30900</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3814,95 +3904,98 @@
       <c r="AI42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2900</v>
       </c>
-      <c r="F43" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G43" s="3">
-        <v>2500</v>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>2500</v>
       </c>
       <c r="I43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>700</v>
       </c>
       <c r="N43" s="3">
         <v>700</v>
       </c>
       <c r="O43" s="3">
+        <v>700</v>
+      </c>
+      <c r="P43" s="3">
         <v>900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>800</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>600</v>
       </c>
       <c r="R43" s="3">
         <v>600</v>
       </c>
       <c r="S43" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="T43" s="3">
         <v>400</v>
       </c>
       <c r="U43" s="3">
+        <v>400</v>
+      </c>
+      <c r="V43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>400</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3915,31 +4008,34 @@
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,8 +4112,11 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4025,58 +4124,58 @@
         <v>400</v>
       </c>
       <c r="E45" s="3">
+        <v>400</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>300</v>
       </c>
       <c r="U45" s="3">
         <v>300</v>
       </c>
       <c r="V45" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="W45" s="3">
         <v>500</v>
@@ -4085,26 +4184,26 @@
         <v>500</v>
       </c>
       <c r="Y45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z45" s="3">
         <v>400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4117,95 +4216,98 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>73800</v>
+        <v>9200</v>
       </c>
       <c r="E46" s="3">
-        <v>75100</v>
+        <v>8900</v>
       </c>
       <c r="F46" s="3">
-        <v>77500</v>
-      </c>
-      <c r="G46" s="3">
-        <v>82900</v>
+        <v>10500</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
-        <v>85000</v>
+        <v>24900</v>
       </c>
       <c r="I46" s="3">
-        <v>90000</v>
+        <v>18100</v>
       </c>
       <c r="J46" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K46" s="3">
         <v>94900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>108300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>62500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>71500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>78500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>34400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>44500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>44200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12000</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,95 +4320,98 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18600</v>
+        <v>77800</v>
       </c>
       <c r="E47" s="3">
-        <v>21900</v>
+        <v>82500</v>
       </c>
       <c r="F47" s="3">
-        <v>14700</v>
-      </c>
-      <c r="G47" s="3">
-        <v>12600</v>
+        <v>86500</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
-        <v>8000</v>
+        <v>70600</v>
       </c>
       <c r="I47" s="3">
-        <v>5300</v>
+        <v>75000</v>
       </c>
       <c r="J47" s="3">
+        <v>84500</v>
+      </c>
+      <c r="K47" s="3">
         <v>5000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>5200</v>
       </c>
       <c r="L47" s="3">
         <v>5200</v>
       </c>
       <c r="M47" s="3">
+        <v>5200</v>
+      </c>
+      <c r="N47" s="3">
         <v>5500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>93000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>93500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>92700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>79100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>78900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>77400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>77700</v>
-      </c>
-      <c r="V47" s="3">
-        <v>77100</v>
       </c>
       <c r="W47" s="3">
         <v>77100</v>
       </c>
       <c r="X47" s="3">
+        <v>77100</v>
+      </c>
+      <c r="Y47" s="3">
         <v>76700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>76200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>29600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>19500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>17600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>11700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13000</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4319,22 +4424,25 @@
       <c r="AI47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2100</v>
       </c>
-      <c r="F48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1700</v>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>1700</v>
@@ -4343,70 +4451,70 @@
         <v>1700</v>
       </c>
       <c r="J48" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="K48" s="3">
         <v>1800</v>
       </c>
       <c r="L48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M48" s="3">
         <v>42200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>42900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>43600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>44100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>44400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>47800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>48300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>48600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>48700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>49200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>49400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>49700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>50100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>50600</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>51000</v>
       </c>
       <c r="AD48" s="3">
         <v>51000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
+      <c r="AE48" s="3">
+        <v>51000</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
@@ -4420,31 +4528,34 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7000</v>
+        <v>4900</v>
       </c>
       <c r="E49" s="3">
-        <v>7000</v>
+        <v>5400</v>
       </c>
       <c r="F49" s="3">
-        <v>1600</v>
+        <v>5500</v>
       </c>
       <c r="G49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>1600</v>
@@ -4486,7 +4597,7 @@
         <v>1600</v>
       </c>
       <c r="X49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="Y49" s="3">
         <v>1700</v>
@@ -4498,14 +4609,14 @@
         <v>1700</v>
       </c>
       <c r="AB49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AC49" s="3">
         <v>1800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1700</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,22 +4840,25 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
@@ -4750,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>1400</v>
@@ -4759,7 +4879,7 @@
         <v>1400</v>
       </c>
       <c r="N52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="O52" s="3">
         <v>1500</v>
@@ -4771,13 +4891,13 @@
         <v>1500</v>
       </c>
       <c r="R52" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="S52" s="3">
         <v>1600</v>
       </c>
       <c r="T52" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="U52" s="3">
         <v>1500</v>
@@ -4786,10 +4906,10 @@
         <v>1500</v>
       </c>
       <c r="W52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X52" s="3">
         <v>1400</v>
-      </c>
-      <c r="X52" s="3">
-        <v>1200</v>
       </c>
       <c r="Y52" s="3">
         <v>1200</v>
@@ -4798,20 +4918,20 @@
         <v>1200</v>
       </c>
       <c r="AA52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>700</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,95 +5048,98 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E54" s="3">
         <v>101600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106100</v>
       </c>
-      <c r="F54" s="3">
-        <v>95500</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3">
         <v>98800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>96400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>98600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>103200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>112800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>122600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>130400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>154100</v>
-      </c>
-      <c r="P54" s="3">
-        <v>146200</v>
       </c>
       <c r="Q54" s="3">
         <v>146200</v>
       </c>
       <c r="R54" s="3">
+        <v>146200</v>
+      </c>
+      <c r="S54" s="3">
         <v>134600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>136300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>137400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>139200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>140400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>142100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>143500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>144200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>116600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>116900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>115100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>77600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>76600</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5026,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,94 +5230,95 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3300</v>
+        <v>2600</v>
       </c>
       <c r="E57" s="3">
-        <v>600</v>
+        <v>2600</v>
       </c>
       <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
+        <v>300</v>
+      </c>
+      <c r="I57" s="3">
+        <v>600</v>
+      </c>
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
-        <v>400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>600</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1200</v>
       </c>
       <c r="N57" s="3">
         <v>1200</v>
       </c>
       <c r="O57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>700</v>
-      </c>
-      <c r="U57" s="3">
-        <v>600</v>
       </c>
       <c r="V57" s="3">
         <v>600</v>
       </c>
       <c r="W57" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="X57" s="3">
         <v>800</v>
       </c>
       <c r="Y57" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>400</v>
       </c>
       <c r="AB57" s="3">
         <v>400</v>
       </c>
       <c r="AC57" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AD57" s="3">
         <v>100</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
+      <c r="AE57" s="3">
+        <v>100</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
@@ -5201,8 +5332,11 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5210,11 +5344,11 @@
         <v>2300</v>
       </c>
       <c r="E58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -5228,23 +5362,23 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>15000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5260,8 +5394,8 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -5302,64 +5436,67 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>100</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>200</v>
+      </c>
+      <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="M59" s="3">
         <v>1900</v>
       </c>
-      <c r="E59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="N59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="O59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="R59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="S59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="T59" s="3">
+        <v>4800</v>
+      </c>
+      <c r="U59" s="3">
         <v>800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>5400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1900</v>
-      </c>
-      <c r="M59" s="3">
-        <v>6900</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>4200</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>10300</v>
-      </c>
-      <c r="R59" s="3">
-        <v>4100</v>
-      </c>
-      <c r="S59" s="3">
-        <v>4800</v>
-      </c>
-      <c r="T59" s="3">
-        <v>800</v>
-      </c>
-      <c r="U59" s="3">
-        <v>600</v>
       </c>
       <c r="V59" s="3">
         <v>600</v>
@@ -5368,29 +5505,29 @@
         <v>600</v>
       </c>
       <c r="X59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y59" s="3">
         <v>200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>300</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5403,8 +5540,11 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5412,86 +5552,86 @@
         <v>7500</v>
       </c>
       <c r="E60" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F60" s="3">
         <v>3300</v>
       </c>
-      <c r="F60" s="3">
-        <v>900</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
         <v>2100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22800</v>
-      </c>
-      <c r="N60" s="3">
-        <v>17300</v>
       </c>
       <c r="O60" s="3">
         <v>17300</v>
       </c>
       <c r="P60" s="3">
+        <v>17300</v>
+      </c>
+      <c r="Q60" s="3">
         <v>4900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1500</v>
-      </c>
-      <c r="U60" s="3">
-        <v>1200</v>
       </c>
       <c r="V60" s="3">
         <v>1200</v>
       </c>
       <c r="W60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X60" s="3">
         <v>1400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>400</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5504,8 +5644,11 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5513,7 +5656,7 @@
         <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -5567,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>14900</v>
@@ -5576,7 +5719,7 @@
         <v>14900</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -5605,34 +5748,37 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="E62" s="3">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3">
-        <v>100</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
       </c>
       <c r="K62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
@@ -5644,7 +5790,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -5656,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
         <v>100</v>
@@ -5665,35 +5811,35 @@
         <v>100</v>
       </c>
       <c r="V62" s="3">
+        <v>100</v>
+      </c>
+      <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD62" s="3">
         <v>24500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>23500</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,95 +6164,98 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>15500</v>
+        <v>10600</v>
       </c>
       <c r="E66" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
+        <v>11100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>3900</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="H66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>17800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15400</v>
-      </c>
-      <c r="U66" s="3">
-        <v>15200</v>
       </c>
       <c r="V66" s="3">
         <v>15200</v>
       </c>
       <c r="W66" s="3">
+        <v>15200</v>
+      </c>
+      <c r="X66" s="3">
         <v>31200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>25300</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>10200</v>
       </c>
       <c r="AA66" s="3">
         <v>10200</v>
       </c>
       <c r="AB66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="AC66" s="3">
         <v>9600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>34700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33200</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,89 +6722,92 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-201700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-197300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-164900</v>
       </c>
-      <c r="F72" s="3">
-        <v>-171000</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>-167300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-168600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-167100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-163900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-165500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-160700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-155100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-170100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-40800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-25900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-17700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-16300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-10900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-8700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-200</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,95 +7138,98 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E76" s="3">
         <v>86100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>104900</v>
-      </c>
-      <c r="F76" s="3">
-        <v>98200</v>
       </c>
       <c r="G76" s="3">
         <v>100300</v>
       </c>
       <c r="H76" s="3">
+        <v>100300</v>
+      </c>
+      <c r="I76" s="3">
         <v>98500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>100100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>103400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>100500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>98100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>102900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>98700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>122300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>126800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>120800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>115600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>116800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>122100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>124100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>125200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>111000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>118000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>118800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>106400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>106700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>105400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>42900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>43400</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7056,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42766</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
-      <c r="AI80" s="2" t="s">
+      <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-32400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-3600</v>
       </c>
       <c r="G81" s="3">
         <v>1200</v>
       </c>
       <c r="H81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-112000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y81" s="3">
         <v>-1000</v>
       </c>
       <c r="Z81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-500</v>
       </c>
       <c r="AC81" s="3">
         <v>-500</v>
       </c>
       <c r="AD81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-100</v>
       </c>
       <c r="AF81" s="3">
         <v>-100</v>
       </c>
       <c r="AG81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH81" s="3">
         <v>300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>100</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,13 +7599,14 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -7428,10 +7627,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>-1100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>400</v>
@@ -7443,16 +7642,16 @@
         <v>400</v>
       </c>
       <c r="P83" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>400</v>
       </c>
       <c r="S83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T83" s="3">
         <v>500</v>
@@ -7467,7 +7666,7 @@
         <v>500</v>
       </c>
       <c r="X83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Y83" s="3">
         <v>400</v>
@@ -7494,16 +7693,19 @@
         <v>400</v>
       </c>
       <c r="AG83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH83" s="3">
         <v>800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>400</v>
       </c>
-      <c r="AI83" s="3" t="s">
+      <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="K89" s="3">
         <v>-2500</v>
       </c>
-      <c r="F89" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-700</v>
       </c>
       <c r="AA89" s="3">
         <v>-700</v>
       </c>
       <c r="AB89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>100</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-200</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8365,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8187,67 +8408,70 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-200</v>
       </c>
       <c r="AE91" s="3">
         <v>-200</v>
       </c>
       <c r="AF91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-700</v>
       </c>
-      <c r="AI91" s="3" t="s">
+      <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
-        <v>-2800</v>
-      </c>
       <c r="F94" s="3">
-        <v>-6800</v>
+        <v>-4800</v>
       </c>
       <c r="G94" s="3">
-        <v>7400</v>
+        <v>-4800</v>
       </c>
       <c r="H94" s="3">
         <v>7400</v>
       </c>
       <c r="I94" s="3">
-        <v>-7600</v>
+        <v>7400</v>
       </c>
       <c r="J94" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="K94" s="3">
         <v>14000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30500</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-26900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>4200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AI94" s="3" t="s">
+      <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9233,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8999,142 +9245,145 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="L100" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>97900</v>
+      </c>
+      <c r="P100" s="3">
+        <v>14500</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>15800</v>
+      </c>
+      <c r="R100" s="3">
+        <v>13800</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>30700</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-900</v>
       </c>
-      <c r="F100" s="3">
-        <v>800</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="K100" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>97900</v>
-      </c>
-      <c r="O100" s="3">
-        <v>14500</v>
-      </c>
-      <c r="P100" s="3">
-        <v>15800</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>13800</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>30700</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>1800</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>900</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>2500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>19300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>18400</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>100</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>200</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
-        <v>100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
-      </c>
       <c r="J101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
@@ -9154,23 +9403,23 @@
         <v>0</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -9189,108 +9438,114 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
-        <v>-6100</v>
-      </c>
       <c r="F102" s="3">
-        <v>-8300</v>
+        <v>-7200</v>
       </c>
       <c r="G102" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="H102" s="3">
         <v>6100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>64500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>9500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>9600</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
   <si>
     <t>RFL</t>
   </si>
@@ -656,169 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AL7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
@@ -842,25 +850,25 @@
         <v>100</v>
       </c>
       <c r="O8" s="3">
+        <v>100</v>
+      </c>
+      <c r="P8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1100</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1200</v>
       </c>
       <c r="V8" s="3">
         <v>1200</v>
@@ -869,61 +877,67 @@
         <v>1200</v>
       </c>
       <c r="X8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z8" s="3">
         <v>1400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>1200</v>
       </c>
       <c r="AC8" s="3">
         <v>1100</v>
       </c>
       <c r="AD8" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="AE8" s="3">
         <v>1100</v>
       </c>
       <c r="AF8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH8" s="3">
         <v>1600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>1300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>2700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ8" s="3" t="s">
+      <c r="AL8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1011,22 +1025,28 @@
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
-      </c>
-      <c r="E10" s="3">
-        <v>300</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -1037,11 +1057,11 @@
       <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
+        <v>100</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
@@ -1115,8 +1135,14 @@
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,92 +1179,94 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F12" s="3">
         <v>1500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>91400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
-        <v>600</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>500</v>
+      </c>
+      <c r="J12" s="3">
         <v>1300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>2200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>3300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>4300</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>3300</v>
       </c>
       <c r="R12" s="3">
         <v>1600</v>
       </c>
       <c r="S12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="U12" s="3">
         <v>500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1000</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1257,8 +1285,14 @@
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,71 +1395,77 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>3500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-8500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J14" s="3">
         <v>-3400</v>
       </c>
-      <c r="H14" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>79100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>7700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>7000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,11 +1478,11 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1465,8 +1505,14 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1477,10 +1523,10 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1510,19 +1556,19 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
         <v>100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>400</v>
-      </c>
-      <c r="T15" s="3">
-        <v>500</v>
-      </c>
-      <c r="U15" s="3">
-        <v>500</v>
       </c>
       <c r="V15" s="3">
         <v>500</v>
@@ -1534,10 +1580,10 @@
         <v>500</v>
       </c>
       <c r="Y15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Z15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AA15" s="3">
         <v>400</v>
@@ -1561,16 +1607,22 @@
         <v>400</v>
       </c>
       <c r="AH15" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="AI15" s="3">
         <v>400</v>
       </c>
-      <c r="AJ15" s="3" t="s">
+      <c r="AJ15" s="3">
+        <v>800</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL15" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1656,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G17" s="3">
         <v>62200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3200</v>
       </c>
-      <c r="G17" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J17" s="3">
         <v>3000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>128900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>13100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>16600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>11800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3100</v>
-      </c>
-      <c r="W17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="X17" s="3">
-        <v>4200</v>
       </c>
       <c r="Y17" s="3">
         <v>2800</v>
       </c>
       <c r="Z17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AB17" s="3">
         <v>2400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>2500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ17" s="3" t="s">
+      <c r="AL17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3100</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-61900</v>
       </c>
       <c r="F18" s="3">
         <v>-3100</v>
       </c>
       <c r="G18" s="3">
+        <v>-61900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-128700</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-2800</v>
       </c>
-      <c r="H18" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-128700</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-12900</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>200</v>
       </c>
-      <c r="AJ18" s="3" t="s">
+      <c r="AL18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,216 +1916,230 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>200</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>4900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-2100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="3" t="s">
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-61800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-5200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-5700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-127800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-10000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-7900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-5200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>1100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>500</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2067,14 +2147,14 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
+        <v>200</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2084,29 +2164,29 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -2114,8 +2194,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2138,11 +2218,11 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
@@ -2150,11 +2230,11 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>0</v>
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
@@ -2162,139 +2242,151 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-64900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>5900</v>
       </c>
-      <c r="G23" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-128300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-11100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-8300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-5700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-1400</v>
       </c>
       <c r="AC23" s="3">
         <v>-700</v>
       </c>
       <c r="AD23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-100</v>
       </c>
-      <c r="AG23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>100</v>
       </c>
-      <c r="AJ23" s="3" t="s">
+      <c r="AL23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-2600</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -2344,34 +2436,40 @@
         <v>0</v>
       </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>8400</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
         <v>0</v>
       </c>
       <c r="AI24" s="3">
         <v>0</v>
       </c>
-      <c r="AJ24" s="3" t="s">
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2572,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-62300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>5900</v>
       </c>
-      <c r="G26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J26" s="3">
         <v>1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-5200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-128300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-11100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-8300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-5700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>1100</v>
       </c>
       <c r="AC26" s="3">
         <v>-700</v>
       </c>
       <c r="AD26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>100</v>
       </c>
-      <c r="AJ26" s="3" t="s">
+      <c r="AL26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-32400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>6000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-111500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-10700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-8200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-5400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>1300</v>
       </c>
       <c r="AC27" s="3">
         <v>-500</v>
       </c>
       <c r="AD27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>100</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AL27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2902,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2804,74 +2926,74 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-100</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>-200</v>
-      </c>
       <c r="K29" s="3">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3">
         <v>-200</v>
       </c>
       <c r="M29" s="3">
+        <v>6700</v>
+      </c>
+      <c r="N29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O29" s="3">
         <v>-600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-1500</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>3</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2890,8 +3012,14 @@
       <c r="AJ29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3122,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3232,234 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-4900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>2100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-32400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>6000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-112000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-12200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-8200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-5400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-1200</v>
       </c>
       <c r="AC33" s="3">
         <v>-500</v>
       </c>
       <c r="AD33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>100</v>
       </c>
-      <c r="AJ33" s="3" t="s">
+      <c r="AL33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3562,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-32400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>6000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-112000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-12200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-8200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-5400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-1200</v>
       </c>
       <c r="AC35" s="3">
         <v>-500</v>
       </c>
       <c r="AD35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>100</v>
       </c>
-      <c r="AJ35" s="3" t="s">
+      <c r="AL35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
-      <c r="AJ38" s="2" t="s">
+      <c r="AL38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3831,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,101 +3871,103 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F41" s="3">
         <v>2700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>21500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>22200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>26500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>29000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>65000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>72400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>6100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>7200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>6200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>8400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>9500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>10800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>12000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>13000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>14800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>10100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>15800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>10600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>12000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>11500</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3803,8 +3977,14 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3830,20 +4010,20 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>71000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>36700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>30400</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3856,11 +4036,11 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3878,20 +4058,20 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>20100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>24700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>30900</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3907,100 +4087,106 @@
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F43" s="3">
         <v>6100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2900</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>2500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3600</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>400</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>200</v>
       </c>
       <c r="AE43" s="3">
         <v>400</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG43" s="3" t="s">
-        <v>3</v>
+      <c r="AF43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>400</v>
       </c>
       <c r="AH43" s="3" t="s">
         <v>3</v>
@@ -4011,8 +4197,14 @@
       <c r="AJ43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,11 +4229,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4115,101 +4307,107 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>44700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>5400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>6000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
-      </c>
-      <c r="W45" s="3">
-        <v>500</v>
-      </c>
-      <c r="X45" s="3">
-        <v>500</v>
       </c>
       <c r="Y45" s="3">
         <v>500</v>
       </c>
       <c r="Z45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AA45" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AB45" s="3">
         <v>400</v>
       </c>
       <c r="AC45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE45" s="3">
         <v>2200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,101 +4417,107 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F46" s="3">
         <v>9200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10500</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3">
         <v>24900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>18100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>94900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>108300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>62500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>71500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>78500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>14800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>6700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>8200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>9800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>9200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>10300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>11700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>13300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>14600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>15700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>34400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>44500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>44200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>12400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>12000</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4323,101 +4527,107 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>53800</v>
+      </c>
+      <c r="F47" s="3">
         <v>77800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>82500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>86500</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>70600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>75000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>84500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>5000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>5200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>5200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>5500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>6000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>93000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>93500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>92700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>79100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>78900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>77400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>77700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>77100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>77100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>76700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>76200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>29600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>19500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>17600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>11700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>13000</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4427,101 +4637,107 @@
       <c r="AJ47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2100</v>
-      </c>
-      <c r="E48" s="3">
-        <v>2200</v>
       </c>
       <c r="F48" s="3">
         <v>2100</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
+      <c r="G48" s="3">
+        <v>2200</v>
       </c>
       <c r="H48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1700</v>
+        <v>2100</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J48" s="3">
         <v>1700</v>
       </c>
       <c r="K48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>42200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>42500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>42900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>43200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>43600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>43800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>44100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>44400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>47800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>48300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>48600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>48700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>49200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>49400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>49700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>50100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>50600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>51000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>51000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,26 +4747,32 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E49" s="3">
         <v>4900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G49" s="3">
         <v>5400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>5500</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -4558,10 +4780,10 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="M49" s="3">
         <v>1600</v>
@@ -4600,10 +4822,10 @@
         <v>1600</v>
       </c>
       <c r="Y49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="Z49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="AA49" s="3">
         <v>1700</v>
@@ -4612,16 +4834,16 @@
         <v>1700</v>
       </c>
       <c r="AC49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="AD49" s="3">
         <v>1700</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF49" s="3" t="s">
-        <v>3</v>
+      <c r="AE49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>1700</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>3</v>
@@ -4635,8 +4857,14 @@
       <c r="AJ49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4967,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +5077,14 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4852,19 +5092,19 @@
         <v>1200</v>
       </c>
       <c r="E52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G52" s="3">
         <v>1100</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -4873,19 +5113,19 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>1400</v>
       </c>
       <c r="O52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="P52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="Q52" s="3">
         <v>1500</v>
@@ -4894,50 +5134,50 @@
         <v>1500</v>
       </c>
       <c r="S52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U52" s="3">
         <v>1600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1600</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1500</v>
-      </c>
-      <c r="V52" s="3">
-        <v>1500</v>
       </c>
       <c r="W52" s="3">
         <v>1500</v>
       </c>
       <c r="X52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>1200</v>
       </c>
       <c r="AA52" s="3">
         <v>1200</v>
       </c>
       <c r="AB52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>700</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4947,8 +5187,14 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,101 +5297,107 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>87800</v>
+      </c>
+      <c r="F54" s="3">
         <v>96800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>101600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>106100</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
         <v>98800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>96400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>98600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>103200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>118300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>112800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>122600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>130400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>154100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>146200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>146200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>134600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>136300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>137400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>139200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>140400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>142100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>143500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>144200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>116600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>116900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>115100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>77600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>76600</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5155,8 +5407,14 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5451,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,101 +5491,103 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>100</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5335,8 +5597,14 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5347,14 +5615,14 @@
         <v>2300</v>
       </c>
       <c r="F58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -5365,26 +5633,26 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>15000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>14900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>14800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>14700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>14500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5397,11 +5665,11 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5439,8 +5707,14 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5448,91 +5722,91 @@
         <v>800</v>
       </c>
       <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>800</v>
+      </c>
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>10300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>4100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>4800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
-      </c>
-      <c r="V59" s="3">
-        <v>600</v>
-      </c>
-      <c r="W59" s="3">
-        <v>600</v>
       </c>
       <c r="X59" s="3">
         <v>600</v>
       </c>
       <c r="Y59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA59" s="3">
         <v>200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>500</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>300</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>400</v>
       </c>
       <c r="AE59" s="3">
         <v>300</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG59" s="3" t="s">
-        <v>3</v>
+      <c r="AF59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>300</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>3</v>
@@ -5543,101 +5817,107 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F60" s="3">
         <v>7500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3300</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
         <v>2100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>21000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>17800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>22800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>17300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>17300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>10800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>700</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>900</v>
       </c>
       <c r="AC60" s="3">
         <v>700</v>
       </c>
       <c r="AD60" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF60" s="3">
         <v>500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>400</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5647,8 +5927,14 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5659,10 +5945,10 @@
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -5713,19 +5999,19 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="Z61" s="3">
         <v>14900</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -5751,40 +6037,46 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F62" s="3">
         <v>3000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -5793,10 +6085,10 @@
         <v>100</v>
       </c>
       <c r="P62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -5805,47 +6097,47 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>100</v>
       </c>
       <c r="W62" s="3">
+        <v>100</v>
+      </c>
+      <c r="X62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>500</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF62" s="3">
         <v>24500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>23500</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5855,8 +6147,14 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6257,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6367,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,101 +6477,107 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F66" s="3">
         <v>10600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>11100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3900</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
         <v>2200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3">
         <v>17800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>19700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>31700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>31800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>19400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>25400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>19000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>19500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>15400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>15200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>15200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>31200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>25500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>25300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>10200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>10200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>9600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>34700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>33200</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6271,8 +6587,14 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6631,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6737,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6847,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6957,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,95 +7067,101 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-215400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-210700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-201700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-197300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-164900</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-167300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-168600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-167100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-163900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-165500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-160700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-155100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-170100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-40800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-28400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-25900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-17700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-16300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-10900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-8700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-7400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6829,8 +7177,14 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7287,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7397,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,101 +7507,107 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>73500</v>
+      </c>
+      <c r="F76" s="3">
         <v>82200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>86100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>104900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>100300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>100300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>98500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>100100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>103400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>100500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>98100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>102900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>98700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>122300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>126800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>120800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>115600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>116800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>122100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>124100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>125200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>111000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>118000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>118800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>106400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>106700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>105400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>42900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>43400</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7245,8 +7617,14 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7727,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
-      <c r="AJ80" s="2" t="s">
+      <c r="AL80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-32400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>6000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-112000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-12200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-8200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-5400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-1200</v>
       </c>
       <c r="AC81" s="3">
         <v>-500</v>
       </c>
       <c r="AD81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>100</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AL81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7996,10 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7630,13 +8028,13 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>-1100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>400</v>
-      </c>
-      <c r="N83" s="3">
-        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
@@ -7645,19 +8043,19 @@
         <v>400</v>
       </c>
       <c r="Q83" s="3">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>400</v>
       </c>
       <c r="S83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T83" s="3">
         <v>400</v>
       </c>
-      <c r="T83" s="3">
-        <v>500</v>
-      </c>
       <c r="U83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V83" s="3">
         <v>500</v>
@@ -7669,10 +8067,10 @@
         <v>500</v>
       </c>
       <c r="Y83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Z83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AA83" s="3">
         <v>400</v>
@@ -7696,16 +8094,22 @@
         <v>400</v>
       </c>
       <c r="AH83" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="AI83" s="3">
         <v>400</v>
       </c>
-      <c r="AJ83" s="3" t="s">
+      <c r="AJ83" s="3">
+        <v>800</v>
+      </c>
+      <c r="AK83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8212,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8322,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8432,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8542,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8652,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-2300</v>
-      </c>
       <c r="H89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-5600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-10400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-7300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-6500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-8600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>100</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ89" s="3" t="s">
+      <c r="AL89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8806,10 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8392,11 +8834,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8411,28 +8853,28 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
       </c>
       <c r="Y91" s="3">
         <v>-300</v>
@@ -8441,37 +8883,43 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ91" s="3" t="s">
+      <c r="AL91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9022,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +9132,124 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>600</v>
       </c>
-      <c r="F94" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-4800</v>
-      </c>
       <c r="H94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="J94" s="3">
         <v>7400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>7400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-7500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>14000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-6400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-30500</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-26900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-8700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-12100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>3600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
       </c>
       <c r="Y94" s="3">
         <v>-300</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>4200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-9400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AJ94" s="3" t="s">
+      <c r="AL94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9286,10 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,11 +9314,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8924,8 +9392,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9502,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9612,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,8 +9722,14 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9248,148 +9740,154 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>800</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="N100" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>97900</v>
+      </c>
+      <c r="R100" s="3">
+        <v>14500</v>
+      </c>
+      <c r="S100" s="3">
+        <v>15800</v>
+      </c>
+      <c r="T100" s="3">
+        <v>13800</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="L100" s="3">
-        <v>6000</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>97900</v>
-      </c>
-      <c r="P100" s="3">
-        <v>14500</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>15800</v>
-      </c>
-      <c r="R100" s="3">
-        <v>13800</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>30700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>1800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>900</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>2500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>19300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>18400</v>
       </c>
-      <c r="AJ100" s="3" t="s">
+      <c r="AL100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
       </c>
       <c r="G101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>100</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
@@ -9406,16 +9904,16 @@
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
       </c>
       <c r="AB101" s="3">
         <v>-100</v>
@@ -9424,7 +9922,7 @@
         <v>0</v>
       </c>
       <c r="AD101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
@@ -9441,111 +9939,123 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
-      <c r="AJ101" s="3" t="s">
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-7200</v>
-      </c>
       <c r="H102" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="J102" s="3">
         <v>6100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>5800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-13200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-41100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-7400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>64500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>8200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>4700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>5200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>9500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ102" s="3" t="s">
+      <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
   <si>
     <t>RFL</t>
   </si>
@@ -656,180 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AM7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>400</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
       </c>
       <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>100</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
@@ -856,22 +859,22 @@
         <v>100</v>
       </c>
       <c r="Q8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
       </c>
       <c r="S8" s="3">
+        <v>200</v>
+      </c>
+      <c r="T8" s="3">
         <v>600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1100</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1200</v>
       </c>
       <c r="W8" s="3">
         <v>1200</v>
@@ -883,46 +886,49 @@
         <v>1200</v>
       </c>
       <c r="Z8" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="AA8" s="3">
         <v>1400</v>
       </c>
       <c r="AB8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC8" s="3">
         <v>1000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1400</v>
       </c>
-      <c r="AL8" s="3" t="s">
+      <c r="AM8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -933,13 +939,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>100</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -1031,25 +1037,28 @@
       <c r="AL9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
       </c>
       <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
         <v>300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>100</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
@@ -1063,8 +1072,8 @@
       <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>100</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
@@ -1141,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,95 +1193,96 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>91400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>100</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>300</v>
       </c>
       <c r="AB12" s="3">
         <v>300</v>
       </c>
       <c r="AC12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD12" s="3">
         <v>400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1000</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1291,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,44 +1417,47 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-8500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1446,29 +1465,29 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>79100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>7700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1484,8 +1503,8 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1511,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1529,7 +1551,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1562,16 +1584,16 @@
         <v>0</v>
       </c>
       <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
         <v>100</v>
-      </c>
-      <c r="T15" s="3">
-        <v>400</v>
       </c>
       <c r="U15" s="3">
         <v>400</v>
       </c>
       <c r="V15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W15" s="3">
         <v>500</v>
@@ -1586,7 +1608,7 @@
         <v>500</v>
       </c>
       <c r="AA15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AB15" s="3">
         <v>400</v>
@@ -1613,16 +1635,19 @@
         <v>400</v>
       </c>
       <c r="AJ15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK15" s="3">
         <v>800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>400</v>
       </c>
-      <c r="AL15" s="3" t="s">
+      <c r="AM15" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E17" s="3">
         <v>3700</v>
-      </c>
-      <c r="E17" s="3">
-        <v>3300</v>
       </c>
       <c r="F17" s="3">
         <v>3300</v>
       </c>
       <c r="G17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H17" s="3">
         <v>62200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>128900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2500</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>1800</v>
       </c>
       <c r="AF17" s="3">
         <v>1800</v>
       </c>
       <c r="AG17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AH17" s="3">
         <v>2200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1200</v>
       </c>
-      <c r="AL17" s="3" t="s">
+      <c r="AM17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3600</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-3100</v>
       </c>
       <c r="F18" s="3">
         <v>-3100</v>
       </c>
       <c r="G18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H18" s="3">
         <v>-61900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-128700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-12900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2800</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-1400</v>
       </c>
       <c r="AB18" s="3">
         <v>-1400</v>
       </c>
       <c r="AC18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>200</v>
       </c>
       <c r="AK18" s="3">
         <v>200</v>
       </c>
-      <c r="AL18" s="3" t="s">
+      <c r="AL18" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,228 +1950,235 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>100</v>
       </c>
       <c r="AF20" s="3">
         <v>100</v>
       </c>
       <c r="AG20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>100</v>
       </c>
       <c r="AJ20" s="3">
         <v>100</v>
       </c>
       <c r="AK20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-61800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-127800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-11900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>-300</v>
       </c>
       <c r="AC21" s="3">
         <v>-300</v>
       </c>
       <c r="AD21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>500</v>
       </c>
-      <c r="AL21" s="3" t="s">
+      <c r="AM21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2153,11 +2192,11 @@
         <v>200</v>
       </c>
       <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2170,35 +2209,35 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>100</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>100</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2224,8 +2263,8 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>3</v>
@@ -2236,8 +2275,8 @@
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
+      <c r="AI22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
@@ -2248,148 +2287,154 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-64900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-128300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-700</v>
       </c>
       <c r="AC23" s="3">
         <v>-700</v>
       </c>
       <c r="AD23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-700</v>
       </c>
       <c r="AF23" s="3">
         <v>-700</v>
       </c>
       <c r="AG23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-100</v>
       </c>
-      <c r="AI23" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3">
         <v>300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>100</v>
       </c>
-      <c r="AL23" s="3" t="s">
+      <c r="AM23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2600</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -2442,20 +2487,20 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>8400</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
         <v>0</v>
       </c>
@@ -2465,11 +2510,14 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
-      <c r="AL24" s="3" t="s">
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-62300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-128300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-700</v>
       </c>
       <c r="AC26" s="3">
         <v>-700</v>
       </c>
       <c r="AD26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE26" s="3">
         <v>1100</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-700</v>
       </c>
       <c r="AF26" s="3">
         <v>-700</v>
       </c>
       <c r="AG26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>-100</v>
       </c>
       <c r="AI26" s="3">
         <v>-100</v>
       </c>
       <c r="AJ26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK26" s="3">
         <v>300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>100</v>
       </c>
-      <c r="AL26" s="3" t="s">
+      <c r="AM26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-32400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-111500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2200</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB27" s="3">
         <v>-1000</v>
       </c>
       <c r="AC27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1300</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-500</v>
       </c>
       <c r="AF27" s="3">
         <v>-500</v>
       </c>
       <c r="AG27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>-100</v>
       </c>
       <c r="AI27" s="3">
         <v>-100</v>
       </c>
       <c r="AJ27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK27" s="3">
         <v>300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>100</v>
       </c>
-      <c r="AL27" s="3" t="s">
+      <c r="AM27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2932,40 +2992,40 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>6700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-600</v>
-      </c>
-      <c r="P29" s="3">
-        <v>-500</v>
       </c>
       <c r="Q29" s="3">
         <v>-500</v>
       </c>
       <c r="R29" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S29" s="3">
         <v>-200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1500</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2973,17 +3033,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>3</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>3</v>
+      <c r="Z29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>3</v>
@@ -2991,12 +3051,12 @@
       <c r="AC29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>3</v>
       </c>
@@ -3018,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-100</v>
       </c>
       <c r="AF32" s="3">
         <v>-100</v>
       </c>
       <c r="AG32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>200</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ32" s="3">
         <v>-100</v>
       </c>
       <c r="AK32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-32400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-112000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-12200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2200</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB33" s="3">
         <v>-1000</v>
       </c>
       <c r="AC33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-500</v>
       </c>
       <c r="AF33" s="3">
         <v>-500</v>
       </c>
       <c r="AG33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>-100</v>
       </c>
       <c r="AI33" s="3">
         <v>-100</v>
       </c>
       <c r="AJ33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK33" s="3">
         <v>300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>100</v>
       </c>
-      <c r="AL33" s="3" t="s">
+      <c r="AM33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-32400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-112000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-12200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2200</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB35" s="3">
         <v>-1000</v>
       </c>
       <c r="AC35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-500</v>
       </c>
       <c r="AF35" s="3">
         <v>-500</v>
       </c>
       <c r="AG35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>-100</v>
       </c>
       <c r="AI35" s="3">
         <v>-100</v>
       </c>
       <c r="AJ35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK35" s="3">
         <v>300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>100</v>
       </c>
-      <c r="AL35" s="3" t="s">
+      <c r="AM35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
-      <c r="AL38" s="2" t="s">
+      <c r="AM38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,104 +3958,105 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E41" s="3">
         <v>48300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7100</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3">
         <v>21500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>65000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>72400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>14800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11500</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3983,8 +4069,11 @@
       <c r="AL41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4016,17 +4105,17 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>71000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>36700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>30400</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4042,8 +4131,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -4064,17 +4153,17 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>20100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>24700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>30900</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4093,104 +4182,107 @@
       <c r="AL42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>16800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2900</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3">
-        <v>2500</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>2500</v>
       </c>
       <c r="L43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M43" s="3">
         <v>600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1000</v>
-      </c>
-      <c r="P43" s="3">
-        <v>700</v>
       </c>
       <c r="Q43" s="3">
         <v>700</v>
       </c>
       <c r="R43" s="3">
+        <v>700</v>
+      </c>
+      <c r="S43" s="3">
         <v>900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>800</v>
-      </c>
-      <c r="T43" s="3">
-        <v>600</v>
       </c>
       <c r="U43" s="3">
         <v>600</v>
       </c>
       <c r="V43" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="W43" s="3">
         <v>400</v>
       </c>
       <c r="X43" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y43" s="3">
         <v>500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>400</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4203,13 +4295,16 @@
       <c r="AL43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>300</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
@@ -4235,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4313,76 +4408,79 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
       </c>
       <c r="H45" s="3">
+        <v>400</v>
+      </c>
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3200</v>
-      </c>
-      <c r="W45" s="3">
-        <v>300</v>
       </c>
       <c r="X45" s="3">
         <v>300</v>
       </c>
       <c r="Y45" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="Z45" s="3">
         <v>500</v>
@@ -4391,26 +4489,26 @@
         <v>500</v>
       </c>
       <c r="AB45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC45" s="3">
         <v>400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>100</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,104 +4521,107 @@
       <c r="AL45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E46" s="3">
         <v>65800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10500</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3">
         <v>24900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>94900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>108300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>62500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>71500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>78500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>34400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>44500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>44200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12000</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4533,104 +4634,107 @@
       <c r="AL46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
         <v>10800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>53800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>77800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>82500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>86500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>70600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>75000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>84500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>5200</v>
       </c>
       <c r="O47" s="3">
         <v>5200</v>
       </c>
       <c r="P47" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Q47" s="3">
         <v>5500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>93000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>93500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>92700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>79100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>78900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>77400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>77700</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>77100</v>
       </c>
       <c r="Z47" s="3">
         <v>77100</v>
       </c>
       <c r="AA47" s="3">
+        <v>77100</v>
+      </c>
+      <c r="AB47" s="3">
         <v>76700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>76200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>29600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>19500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>17600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>11700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13000</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4643,31 +4747,34 @@
       <c r="AL47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1900</v>
-      </c>
-      <c r="E48" s="3">
-        <v>2100</v>
       </c>
       <c r="F48" s="3">
         <v>2100</v>
       </c>
       <c r="G48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H48" s="3">
         <v>2200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2100</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1700</v>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>1700</v>
@@ -4676,70 +4783,70 @@
         <v>1700</v>
       </c>
       <c r="M48" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="N48" s="3">
         <v>1800</v>
       </c>
       <c r="O48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P48" s="3">
         <v>42200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>43200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>43600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>43800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>44100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>44400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>47800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>48300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>48600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>48700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>49200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>49400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>49700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>50100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>50600</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>51000</v>
       </c>
       <c r="AG48" s="3">
         <v>51000</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>3</v>
+      <c r="AH48" s="3">
+        <v>51000</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>3</v>
@@ -4753,29 +4860,32 @@
       <c r="AL48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1800</v>
-      </c>
-      <c r="E49" s="3">
-        <v>4900</v>
       </c>
       <c r="F49" s="3">
         <v>4900</v>
       </c>
       <c r="G49" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H49" s="3">
         <v>5400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5500</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -4786,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>1600</v>
@@ -4828,7 +4938,7 @@
         <v>1600</v>
       </c>
       <c r="AA49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="AB49" s="3">
         <v>1700</v>
@@ -4840,14 +4950,14 @@
         <v>1700</v>
       </c>
       <c r="AE49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AF49" s="3">
         <v>1800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1700</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4863,8 +4973,11 @@
       <c r="AL49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,13 +5199,16 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="E52" s="3">
         <v>1200</v>
@@ -5098,16 +5217,16 @@
         <v>1200</v>
       </c>
       <c r="G52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -5119,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>1400</v>
@@ -5128,7 +5247,7 @@
         <v>1400</v>
       </c>
       <c r="Q52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="R52" s="3">
         <v>1500</v>
@@ -5140,13 +5259,13 @@
         <v>1500</v>
       </c>
       <c r="U52" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="V52" s="3">
         <v>1600</v>
       </c>
       <c r="W52" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="X52" s="3">
         <v>1500</v>
@@ -5155,10 +5274,10 @@
         <v>1500</v>
       </c>
       <c r="Z52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>1200</v>
       </c>
       <c r="AB52" s="3">
         <v>1200</v>
@@ -5167,20 +5286,20 @@
         <v>1200</v>
       </c>
       <c r="AD52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AE52" s="3">
         <v>1100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>700</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5193,8 +5312,11 @@
       <c r="AL52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,104 +5425,107 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>108100</v>
+      </c>
+      <c r="E54" s="3">
         <v>83000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>96800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>101600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>106100</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3">
         <v>98800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>96400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>98600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>103200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>118300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>112800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>122600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>130400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>154100</v>
-      </c>
-      <c r="S54" s="3">
-        <v>146200</v>
       </c>
       <c r="T54" s="3">
         <v>146200</v>
       </c>
       <c r="U54" s="3">
+        <v>146200</v>
+      </c>
+      <c r="V54" s="3">
         <v>134600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>136300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>137400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>139200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>140400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>142100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>143500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>144200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>116600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>116900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>115100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>77600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>76600</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5538,11 @@
       <c r="AL54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,103 +5622,104 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
-      </c>
-      <c r="F57" s="3">
-        <v>2600</v>
       </c>
       <c r="G57" s="3">
         <v>2600</v>
       </c>
       <c r="H57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1200</v>
       </c>
       <c r="Q57" s="3">
         <v>1200</v>
       </c>
       <c r="R57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>700</v>
-      </c>
-      <c r="X57" s="3">
-        <v>600</v>
       </c>
       <c r="Y57" s="3">
         <v>600</v>
       </c>
       <c r="Z57" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="AA57" s="3">
         <v>800</v>
       </c>
       <c r="AB57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>300</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>400</v>
       </c>
       <c r="AE57" s="3">
         <v>400</v>
       </c>
       <c r="AF57" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AG57" s="3">
         <v>100</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>3</v>
+      <c r="AH57" s="3">
+        <v>100</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>3</v>
@@ -5603,13 +5733,16 @@
       <c r="AL57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2300</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
         <v>2300</v>
@@ -5621,11 +5754,11 @@
         <v>2300</v>
       </c>
       <c r="H58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I58" s="3">
         <v>1700</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -5639,23 +5772,23 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>15000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14500</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5671,8 +5804,8 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5713,73 +5846,76 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>1000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>200</v>
       </c>
       <c r="L59" s="3">
         <v>200</v>
       </c>
       <c r="M59" s="3">
+        <v>200</v>
+      </c>
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
-      </c>
-      <c r="X59" s="3">
-        <v>600</v>
       </c>
       <c r="Y59" s="3">
         <v>600</v>
@@ -5788,29 +5924,29 @@
         <v>600</v>
       </c>
       <c r="AA59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB59" s="3">
         <v>200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>300</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5823,104 +5959,107 @@
       <c r="AL59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7200</v>
-      </c>
-      <c r="F60" s="3">
-        <v>7500</v>
       </c>
       <c r="G60" s="3">
         <v>7500</v>
       </c>
       <c r="H60" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I60" s="3">
         <v>3300</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>2100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22800</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>17300</v>
       </c>
       <c r="R60" s="3">
         <v>17300</v>
       </c>
       <c r="S60" s="3">
+        <v>17300</v>
+      </c>
+      <c r="T60" s="3">
         <v>4900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1500</v>
-      </c>
-      <c r="X60" s="3">
-        <v>1200</v>
       </c>
       <c r="Y60" s="3">
         <v>1200</v>
       </c>
       <c r="Z60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA60" s="3">
         <v>1400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>400</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5933,8 +6072,11 @@
       <c r="AL60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5951,7 +6093,7 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -6005,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="AA61" s="3">
         <v>14900</v>
@@ -6014,7 +6156,7 @@
         <v>14900</v>
       </c>
       <c r="AC61" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
@@ -6043,43 +6185,46 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E62" s="3">
         <v>3300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3">
-        <v>100</v>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>100</v>
       </c>
       <c r="L62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -6091,7 +6236,7 @@
         <v>100</v>
       </c>
       <c r="R62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -6103,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W62" s="3">
         <v>100</v>
@@ -6112,35 +6257,35 @@
         <v>100</v>
       </c>
       <c r="Y62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z62" s="3">
         <v>200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>500</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG62" s="3">
         <v>24500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>23500</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6153,8 +6298,11 @@
       <c r="AL62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,104 +6637,107 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10500</v>
+        <v>23600</v>
       </c>
       <c r="E66" s="3">
         <v>10500</v>
       </c>
       <c r="F66" s="3">
+        <v>10500</v>
+      </c>
+      <c r="G66" s="3">
         <v>10600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3900</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
         <v>2200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3">
         <v>17800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15400</v>
-      </c>
-      <c r="X66" s="3">
-        <v>15200</v>
       </c>
       <c r="Y66" s="3">
         <v>15200</v>
       </c>
       <c r="Z66" s="3">
+        <v>15200</v>
+      </c>
+      <c r="AA66" s="3">
         <v>31200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>25500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>25300</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>10200</v>
       </c>
       <c r="AD66" s="3">
         <v>10200</v>
       </c>
       <c r="AE66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="AF66" s="3">
         <v>9600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>34700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33200</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6593,8 +6750,11 @@
       <c r="AL66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,98 +7243,101 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-220200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-215400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-210700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-201700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-197300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-164900</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>-167300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-168600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-167100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-163900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-165500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-160700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-155100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-170100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-40800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-28400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-25900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-17700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-16300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-10900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-200</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7183,8 +7356,11 @@
       <c r="AL72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,104 +7695,107 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E76" s="3">
         <v>69400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>73500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>82200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>86100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>104900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>100300</v>
       </c>
       <c r="J76" s="3">
         <v>100300</v>
       </c>
       <c r="K76" s="3">
+        <v>100300</v>
+      </c>
+      <c r="L76" s="3">
         <v>98500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>100100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>103400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>100500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>98100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>102900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>98700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>122300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>126800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>120800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>115600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>116800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>122100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>124100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>125200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>111000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>118000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>118800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>106400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>106700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>105400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>42900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>43400</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7623,8 +7808,11 @@
       <c r="AL76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
-      <c r="AL80" s="2" t="s">
+      <c r="AM80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-32400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-112000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-12200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2200</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB81" s="3">
         <v>-1000</v>
       </c>
       <c r="AC81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-500</v>
       </c>
       <c r="AF81" s="3">
         <v>-500</v>
       </c>
       <c r="AG81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-9300</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>-100</v>
       </c>
       <c r="AI81" s="3">
         <v>-100</v>
       </c>
       <c r="AJ81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK81" s="3">
         <v>300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>100</v>
       </c>
-      <c r="AL81" s="3" t="s">
+      <c r="AM81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,13 +8195,14 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -8034,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>-1100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>400</v>
@@ -8049,16 +8247,16 @@
         <v>400</v>
       </c>
       <c r="S83" s="3">
+        <v>400</v>
+      </c>
+      <c r="T83" s="3">
         <v>1100</v>
-      </c>
-      <c r="T83" s="3">
-        <v>400</v>
       </c>
       <c r="U83" s="3">
         <v>400</v>
       </c>
       <c r="V83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W83" s="3">
         <v>500</v>
@@ -8073,7 +8271,7 @@
         <v>500</v>
       </c>
       <c r="AA83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AB83" s="3">
         <v>400</v>
@@ -8100,16 +8298,19 @@
         <v>400</v>
       </c>
       <c r="AJ83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK83" s="3">
         <v>800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>400</v>
       </c>
-      <c r="AL83" s="3" t="s">
+      <c r="AM83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-700</v>
       </c>
       <c r="AD89" s="3">
         <v>-700</v>
       </c>
       <c r="AE89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>100</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
-      </c>
       <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-200</v>
       </c>
-      <c r="AL89" s="3" t="s">
+      <c r="AM89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8840,8 +9060,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8859,67 +9079,70 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-500</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-200</v>
       </c>
       <c r="AH91" s="3">
         <v>-200</v>
       </c>
       <c r="AI91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-700</v>
       </c>
-      <c r="AL91" s="3" t="s">
+      <c r="AM91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E94" s="3">
         <v>42500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>8600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6800</v>
-      </c>
-      <c r="J94" s="3">
-        <v>7400</v>
       </c>
       <c r="K94" s="3">
         <v>7400</v>
       </c>
       <c r="L94" s="3">
+        <v>7400</v>
+      </c>
+      <c r="M94" s="3">
         <v>-7500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-30500</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-26900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>3600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>4200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-9400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AL94" s="3" t="s">
+      <c r="AM94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9320,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9398,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9746,47 +9991,47 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>97900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>14500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>15800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13800</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -9794,11 +10039,11 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -9806,91 +10051,94 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>30700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>900</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>2500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>19300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>18400</v>
       </c>
-      <c r="AL100" s="3" t="s">
+      <c r="AM100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-100</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
       </c>
       <c r="K101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N101" s="3">
         <v>-100</v>
       </c>
       <c r="O101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
@@ -9910,23 +10158,23 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
@@ -9945,117 +10193,123 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
-      <c r="AL101" s="3" t="s">
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E102" s="3">
         <v>40200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>64500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AH102" s="3">
-        <v>0</v>
-      </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>9500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>9600</v>
       </c>
-      <c r="AL102" s="3" t="s">
+      <c r="AM102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
   <si>
     <t>RFL</t>
   </si>
@@ -656,196 +656,204 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43951</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43769</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43677</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43585</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43496</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43404</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43312</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43220</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43131</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42947</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42766</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42674</v>
       </c>
-      <c r="AN7" s="2" t="s">
+      <c r="AP7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>200</v>
+      </c>
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>100</v>
-      </c>
-      <c r="K8" s="3">
-        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>100</v>
@@ -869,25 +877,25 @@
         <v>100</v>
       </c>
       <c r="S8" s="3">
+        <v>100</v>
+      </c>
+      <c r="T8" s="3">
+        <v>100</v>
+      </c>
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1100</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1200</v>
       </c>
       <c r="Z8" s="3">
         <v>1200</v>
@@ -896,46 +904,52 @@
         <v>1200</v>
       </c>
       <c r="AB8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AD8" s="3">
         <v>1400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1000</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>1200</v>
       </c>
       <c r="AG8" s="3">
         <v>1100</v>
       </c>
       <c r="AH8" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="AI8" s="3">
         <v>1100</v>
       </c>
       <c r="AJ8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AL8" s="3">
         <v>1600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>1300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>2700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>1400</v>
       </c>
-      <c r="AN8" s="3" t="s">
+      <c r="AP8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -952,17 +966,17 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1050,34 +1064,40 @@
       <c r="AN9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>200</v>
+      </c>
+      <c r="F10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>100</v>
-      </c>
-      <c r="H10" s="3">
-        <v>100</v>
-      </c>
-      <c r="I10" s="3">
-        <v>300</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
       </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L10" s="3">
         <v>100</v>
@@ -1088,11 +1108,11 @@
       <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
+        <v>100</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
@@ -1166,8 +1186,14 @@
       <c r="AN10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,104 +1234,106 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>7500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G12" s="3">
         <v>3000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>91400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>3300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>4300</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="U12" s="3">
-        <v>3300</v>
       </c>
       <c r="V12" s="3">
         <v>1600</v>
       </c>
       <c r="W12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="X12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Y12" s="3">
         <v>500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1000</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1324,8 +1352,14 @@
       <c r="AN12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,83 +1474,89 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J14" s="3">
         <v>2300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>3500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-8500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>1700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-3400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>79100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>7700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>7000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1529,11 +1569,11 @@
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1556,8 +1596,14 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1580,10 +1626,10 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1613,19 +1659,19 @@
         <v>0</v>
       </c>
       <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
         <v>100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>400</v>
-      </c>
-      <c r="X15" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>500</v>
       </c>
       <c r="Z15" s="3">
         <v>500</v>
@@ -1637,10 +1683,10 @@
         <v>500</v>
       </c>
       <c r="AC15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AD15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AE15" s="3">
         <v>400</v>
@@ -1664,16 +1710,22 @@
         <v>400</v>
       </c>
       <c r="AL15" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="AM15" s="3">
         <v>400</v>
       </c>
-      <c r="AN15" s="3" t="s">
+      <c r="AN15" s="3">
+        <v>800</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AP15" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1763,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F17" s="3">
         <v>12100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J17" s="3">
         <v>3300</v>
       </c>
-      <c r="H17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>62200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>128900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>13100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>16600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>11800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3100</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>4200</v>
       </c>
       <c r="AC17" s="3">
         <v>2800</v>
       </c>
       <c r="AD17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AF17" s="3">
         <v>2400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>1800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>1500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>1400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>2500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1200</v>
       </c>
-      <c r="AN17" s="3" t="s">
+      <c r="AP17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-11800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-5900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-3100</v>
-      </c>
       <c r="I18" s="3">
-        <v>-61900</v>
+        <v>-3700</v>
       </c>
       <c r="J18" s="3">
         <v>-3100</v>
       </c>
       <c r="K18" s="3">
+        <v>-61900</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="M18" s="3">
         <v>-2500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-4000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-128700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-12900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-16000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-10800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>200</v>
       </c>
-      <c r="AN18" s="3" t="s">
+      <c r="AP18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,240 +2051,254 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
+        <v>200</v>
+      </c>
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>2400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>100</v>
       </c>
-      <c r="AM20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="3" t="s">
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-11500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-5700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="O21" s="3">
         <v>-3000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-61800</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-5200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-4600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-127800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-11900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-10000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-7900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>1100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>500</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AP21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2238,14 +2318,14 @@
         <v>200</v>
       </c>
       <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2255,29 +2335,29 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -2285,8 +2365,8 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2309,11 +2389,11 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH22" s="3" t="s">
-        <v>3</v>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>3</v>
@@ -2321,11 +2401,11 @@
       <c r="AJ22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>0</v>
+      <c r="AK22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AM22" s="3">
         <v>0</v>
@@ -2333,163 +2413,175 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-12200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-6500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-9200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-64900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>5900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-5000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-128300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-12300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-11100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-8300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-700</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>-1400</v>
       </c>
       <c r="AG23" s="3">
         <v>-700</v>
       </c>
       <c r="AH23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AK23" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-100</v>
       </c>
-      <c r="AK23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="3">
         <v>300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>100</v>
       </c>
-      <c r="AN23" s="3" t="s">
+      <c r="AP23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-2400</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-2600</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -2539,34 +2631,40 @@
         <v>0</v>
       </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3">
-        <v>0</v>
-      </c>
       <c r="AL24" s="3">
         <v>0</v>
       </c>
       <c r="AM24" s="3">
         <v>0</v>
       </c>
-      <c r="AN24" s="3" t="s">
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2779,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-12100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-9200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-62300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>5900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-5000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-128300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-12300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-11100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-8300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-700</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>1100</v>
       </c>
       <c r="AG26" s="3">
         <v>-700</v>
       </c>
       <c r="AH26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-9300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>100</v>
       </c>
-      <c r="AN26" s="3" t="s">
+      <c r="AP26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-12100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-9000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-32400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-5000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-111500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-12200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-10700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-8200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>1300</v>
       </c>
       <c r="AG27" s="3">
         <v>-500</v>
       </c>
       <c r="AH27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-9300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>100</v>
       </c>
-      <c r="AN27" s="3" t="s">
+      <c r="AP27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3145,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3059,74 +3181,74 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-100</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>-200</v>
-      </c>
       <c r="O29" s="3">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="P29" s="3">
         <v>-200</v>
       </c>
       <c r="Q29" s="3">
+        <v>6700</v>
+      </c>
+      <c r="R29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S29" s="3">
         <v>-600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>-500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-1500</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>3</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>3</v>
       </c>
@@ -3145,8 +3267,14 @@
       <c r="AN29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3389,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3511,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-2400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>2100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-100</v>
       </c>
-      <c r="AM32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN32" s="3" t="s">
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-12100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-9000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-32400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-5500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-112000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-12400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-12200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-8200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>-1200</v>
       </c>
       <c r="AG33" s="3">
         <v>-500</v>
       </c>
       <c r="AH33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-9300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>100</v>
       </c>
-      <c r="AN33" s="3" t="s">
+      <c r="AP33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3877,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-12100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-9000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-32400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-5500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-112000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-12400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-12200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-8200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>-1200</v>
       </c>
       <c r="AG35" s="3">
         <v>-500</v>
       </c>
       <c r="AH35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-9300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>100</v>
       </c>
-      <c r="AN35" s="3" t="s">
+      <c r="AP35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43951</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43769</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43677</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43585</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43496</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43404</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43312</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43220</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43131</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42947</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42766</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42674</v>
       </c>
-      <c r="AN38" s="2" t="s">
+      <c r="AP38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4174,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,113 +4218,115 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>45500</v>
+      </c>
+      <c r="F41" s="3">
         <v>52800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>37900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>48300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3">
         <v>21500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>15400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>22200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>26500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>29000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>65000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>72400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>7900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>6100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>7200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>6200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>8400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>9500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>10800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>12000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>13000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>14800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>10100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>15800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>10600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>12000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>11500</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4162,8 +4336,14 @@
       <c r="AN41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4201,20 +4381,20 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>71000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>36700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>30400</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4227,11 +4407,11 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -4249,20 +4429,20 @@
         <v>0</v>
       </c>
       <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
         <v>20100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>24700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>30900</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4278,112 +4458,118 @@
       <c r="AN42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
         <v>400</v>
       </c>
       <c r="F43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G43" s="3">
+        <v>400</v>
+      </c>
+      <c r="H43" s="3">
         <v>16800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>13200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>6100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
         <v>2500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>4000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>3600</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>400</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>200</v>
       </c>
       <c r="AI43" s="3">
         <v>400</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK43" s="3" t="s">
-        <v>3</v>
+      <c r="AJ43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK43" s="3">
+        <v>400</v>
       </c>
       <c r="AL43" s="3" t="s">
         <v>3</v>
@@ -4394,8 +4580,14 @@
       <c r="AN43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4405,11 +4597,11 @@
       <c r="E44" s="3">
         <v>300</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+      <c r="F44" s="3">
+        <v>300</v>
+      </c>
+      <c r="G44" s="3">
+        <v>300</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -4432,11 +4624,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4510,113 +4702,119 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>44700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>5800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>5400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>6000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>3200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>500</v>
       </c>
       <c r="AC45" s="3">
         <v>500</v>
       </c>
       <c r="AD45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AE45" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AF45" s="3">
         <v>400</v>
       </c>
       <c r="AG45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI45" s="3">
         <v>2200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>100</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4626,113 +4824,119 @@
       <c r="AN45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>48300</v>
+      </c>
+      <c r="F46" s="3">
         <v>56700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>42400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>65800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>24300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>9200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>8900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10500</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3">
         <v>24900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>18100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>10800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>94900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>108300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>62500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>71500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>78500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>14800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>6000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>6700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>8200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>9800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>9200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>10300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>11700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>13300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>14600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>15700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>34400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>44500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>44200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>12400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4742,113 +4946,119 @@
       <c r="AN46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="D47" s="3">
+        <v>800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>500</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>10800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>53800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>77800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>82500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>86500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>70600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>75000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>84500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>5000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>5200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>5200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>5500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>6000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>93000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>93500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>92700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>79100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>78900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>77400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>77700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>77100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>77100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>76700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>76200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>29600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>19500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>17600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>11700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4858,113 +5068,119 @@
       <c r="AN47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="E48" s="3">
         <v>1600</v>
       </c>
       <c r="F48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H48" s="3">
         <v>1900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2100</v>
-      </c>
-      <c r="H48" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2200</v>
       </c>
       <c r="J48" s="3">
         <v>2100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
+      <c r="K48" s="3">
+        <v>2200</v>
       </c>
       <c r="L48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1700</v>
+        <v>2100</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>1700</v>
       </c>
       <c r="O48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>42200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>42500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>42900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>43200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>43600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>43800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>44100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>44400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>47800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>48300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>48600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>48700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>49200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>49400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>49700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>50100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>50600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>51000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>51000</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4974,8 +5190,14 @@
       <c r="AN48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4983,29 +5205,29 @@
         <v>20900</v>
       </c>
       <c r="E49" s="3">
+        <v>20900</v>
+      </c>
+      <c r="F49" s="3">
+        <v>20900</v>
+      </c>
+      <c r="G49" s="3">
         <v>29300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>5400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>5500</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
@@ -5013,10 +5235,10 @@
         <v>0</v>
       </c>
       <c r="O49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="3">
         <v>1600</v>
@@ -5055,10 +5277,10 @@
         <v>1600</v>
       </c>
       <c r="AC49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="AD49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="AE49" s="3">
         <v>1700</v>
@@ -5067,16 +5289,16 @@
         <v>1700</v>
       </c>
       <c r="AG49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="AH49" s="3">
         <v>1700</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ49" s="3" t="s">
-        <v>3</v>
+      <c r="AI49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AJ49" s="3">
+        <v>1700</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>3</v>
@@ -5090,8 +5312,14 @@
       <c r="AN49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5434,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,40 +5556,46 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F52" s="3">
         <v>3300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1200</v>
       </c>
       <c r="H52" s="3">
         <v>1200</v>
       </c>
       <c r="I52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K52" s="3">
         <v>1100</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -5364,19 +5604,19 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>1400</v>
       </c>
       <c r="S52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="T52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="U52" s="3">
         <v>1500</v>
@@ -5385,50 +5625,50 @@
         <v>1500</v>
       </c>
       <c r="W52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1600</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>1500</v>
       </c>
       <c r="AA52" s="3">
         <v>1500</v>
       </c>
       <c r="AB52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1400</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>1200</v>
       </c>
       <c r="AE52" s="3">
         <v>1200</v>
       </c>
       <c r="AF52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH52" s="3">
         <v>1100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>700</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5438,8 +5678,14 @@
       <c r="AN52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,113 +5800,119 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>105400</v>
+      </c>
+      <c r="F54" s="3">
         <v>114100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>108100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>83000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>87800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>96800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>101600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>106100</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3">
         <v>98800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>96400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>98600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>103200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>118300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>112800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>122600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>130400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>154100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>146200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>146200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>134600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>136300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>137400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>139200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>140400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>142100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>143500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>144200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>116600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>116900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>115100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>77600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>76600</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5670,8 +5922,14 @@
       <c r="AN54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5970,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,113 +6014,115 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F57" s="3">
         <v>6900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>100</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5870,8 +6132,14 @@
       <c r="AN57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5882,10 +6150,10 @@
         <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>2300</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>2300</v>
+        <v>600</v>
       </c>
       <c r="H58" s="3">
         <v>2300</v>
@@ -5894,14 +6162,14 @@
         <v>2300</v>
       </c>
       <c r="J58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L58" s="3">
         <v>1700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5912,26 +6180,26 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>15000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>14900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>14800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>14700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>14500</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5944,11 +6212,11 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5986,112 +6254,118 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
       </c>
       <c r="F59" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H59" s="3">
         <v>800</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>800</v>
+      </c>
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>6900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>4200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>10300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>4100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>4800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>800</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>600</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>600</v>
       </c>
       <c r="AB59" s="3">
         <v>600</v>
       </c>
       <c r="AC59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE59" s="3">
         <v>200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>500</v>
-      </c>
-      <c r="AG59" s="3">
-        <v>300</v>
-      </c>
-      <c r="AH59" s="3">
-        <v>400</v>
       </c>
       <c r="AI59" s="3">
         <v>300</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK59" s="3" t="s">
-        <v>3</v>
+      <c r="AJ59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK59" s="3">
+        <v>300</v>
       </c>
       <c r="AL59" s="3" t="s">
         <v>3</v>
@@ -6102,113 +6376,119 @@
       <c r="AN59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F60" s="3">
         <v>11600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>11000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3300</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3">
         <v>2100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>21000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>17800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>22800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>17300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>17300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>10800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>5300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>5700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>700</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>900</v>
       </c>
       <c r="AG60" s="3">
         <v>700</v>
       </c>
       <c r="AH60" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>400</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL60" s="3" t="s">
         <v>3</v>
       </c>
@@ -6218,8 +6498,14 @@
       <c r="AN60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6242,10 +6528,10 @@
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -6296,19 +6582,19 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="AC61" s="3">
-        <v>14900</v>
+        <v>0</v>
       </c>
       <c r="AD61" s="3">
         <v>14900</v>
       </c>
       <c r="AE61" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="AF61" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
@@ -6334,52 +6620,58 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E62" s="3">
         <v>3900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G62" s="3">
         <v>3500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>100</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
       <c r="O62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
@@ -6388,10 +6680,10 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -6400,47 +6692,47 @@
         <v>0</v>
       </c>
       <c r="X62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3">
         <v>100</v>
       </c>
       <c r="AA62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC62" s="3">
         <v>200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>500</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>24500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>23500</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6450,8 +6742,14 @@
       <c r="AN62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6864,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6986,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,113 +7108,119 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F66" s="3">
         <v>15700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>23600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>10500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>10500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>10600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3900</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3">
         <v>2200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3">
         <v>17800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>14600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>19700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>31700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>31800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>19400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>25400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>19000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>19500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>15400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>15200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>15200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>31200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>25500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>25300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>10200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>10200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>9600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>34700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>33200</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6914,8 +7230,14 @@
       <c r="AN66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7278,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7396,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7518,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7640,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,107 +7762,113 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-248500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-242100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-232300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-220200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-215400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-210700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-201700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-197300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-164900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>-167300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-168600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-167100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-163900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-165500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-160700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-155100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-170100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-40800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-28400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-25900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-17700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-200</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7536,8 +7884,14 @@
       <c r="AN72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8006,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8128,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,113 +8250,119 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>85200</v>
+      </c>
+      <c r="F76" s="3">
         <v>94400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>80600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>69400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>73500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>82200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>86100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>104900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>100300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>100300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>98500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>100100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>103400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>100500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>98100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>102900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>98700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>122300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>126800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>120800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>115600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>116800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>122100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>124100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>125200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>111000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>118000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>118800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>106400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>106700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>105400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>42900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>43400</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL76" s="3" t="s">
         <v>3</v>
       </c>
@@ -8000,8 +8372,14 @@
       <c r="AN76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8494,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43951</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43769</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43677</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43585</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43496</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43404</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43312</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43220</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43131</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42947</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42766</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42674</v>
       </c>
-      <c r="AN80" s="2" t="s">
+      <c r="AP80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-12100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-9000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-32400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-5500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-112000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-12400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-12200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-8200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>-1200</v>
       </c>
       <c r="AG81" s="3">
         <v>-500</v>
       </c>
       <c r="AH81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-9300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>100</v>
       </c>
-      <c r="AN81" s="3" t="s">
+      <c r="AP81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,23 +8791,25 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
@@ -8437,13 +8835,13 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>400</v>
       </c>
       <c r="S83" s="3">
         <v>400</v>
@@ -8452,19 +8850,19 @@
         <v>400</v>
       </c>
       <c r="U83" s="3">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="V83" s="3">
         <v>400</v>
       </c>
       <c r="W83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X83" s="3">
         <v>400</v>
       </c>
-      <c r="X83" s="3">
-        <v>500</v>
-      </c>
       <c r="Y83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z83" s="3">
         <v>500</v>
@@ -8476,10 +8874,10 @@
         <v>500</v>
       </c>
       <c r="AC83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AD83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AE83" s="3">
         <v>400</v>
@@ -8503,16 +8901,22 @@
         <v>400</v>
       </c>
       <c r="AL83" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="AM83" s="3">
         <v>400</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AN83" s="3">
+        <v>800</v>
+      </c>
+      <c r="AO83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AP83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9031,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9153,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9275,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9397,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9519,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-10400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-5600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-10400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-7300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-6500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-7000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-8600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>100</v>
       </c>
-      <c r="AI89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>-200</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AP89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,8 +9689,10 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9287,11 +9729,11 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9306,28 +9748,28 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
       </c>
       <c r="AC91" s="3">
         <v>-300</v>
@@ -9336,37 +9778,43 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-700</v>
       </c>
-      <c r="AN91" s="3" t="s">
+      <c r="AP91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9929,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +10051,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-7200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>42500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>8600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-6800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>7400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>7400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-7500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>14000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-30500</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-26900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-8700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-12100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>3600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-500</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
       </c>
       <c r="AC94" s="3">
         <v>-300</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>4200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-9400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AP94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +10221,10 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,11 +10261,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9871,8 +10339,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10461,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10583,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,20 +10705,26 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>24900</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -10243,100 +10735,106 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-15000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>6000</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>97900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>14500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>15800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>13800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>30700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>1800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>900</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3">
         <v>2500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>19300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>18400</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AP100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10344,59 +10842,59 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
-      </c>
-      <c r="H101" s="3">
-        <v>100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-300</v>
       </c>
       <c r="J101" s="3">
         <v>100</v>
       </c>
       <c r="K101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L101" s="3">
+        <v>100</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
@@ -10413,16 +10911,16 @@
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
       </c>
       <c r="AF101" s="3">
         <v>-100</v>
@@ -10431,7 +10929,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI101" s="3">
         <v>0</v>
@@ -10448,123 +10946,135 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
-      <c r="AN101" s="3" t="s">
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F102" s="3">
         <v>14800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-10400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>40200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-8300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-13200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-41100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-7400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>64500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>8200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>4700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>5200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>-100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>9500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>9600</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AP102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>RFL</t>
   </si>
@@ -1241,8 +1241,8 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>4500</v>
       </c>
       <c r="E12" s="3">
         <v>7500</v>
@@ -1498,7 +1498,7 @@
         <v>1000</v>
       </c>
       <c r="H14" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="I14" s="3">
         <v>5900</v>
@@ -1783,7 +1783,7 @@
         <v>6300</v>
       </c>
       <c r="H17" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="I17" s="3">
         <v>3900</v>
@@ -1905,7 +1905,7 @@
         <v>-5900</v>
       </c>
       <c r="H18" s="3">
-        <v>-3600</v>
+        <v>-3500</v>
       </c>
       <c r="I18" s="3">
         <v>-3700</v>
@@ -2193,7 +2193,7 @@
         <v>-5700</v>
       </c>
       <c r="H21" s="3">
-        <v>-3600</v>
+        <v>-3500</v>
       </c>
       <c r="I21" s="3">
         <v>-3700</v>
@@ -6266,7 +6266,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
